--- a/data/exports/王颖瑜伽/dist_order_2026-08-18.xlsx
+++ b/data/exports/王颖瑜伽/dist_order_2026-08-18.xlsx
@@ -125,11 +125,11 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="0">
-        <v>49337893</v>
+        <v>49340095</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>郑洁玲</t>
+          <t>小小</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -154,7 +154,7 @@
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:36:14</t>
+          <t>2026-08-18 00:24:20</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -184,17 +184,17 @@
       </c>
       <c r="M2" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608171736033078</t>
+          <t>4500000339202608185905136033</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="0">
-        <v>49337886</v>
+        <v>49340080</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>浪漫樱花</t>
+          <t>封艳丽</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -219,7 +219,7 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:44</t>
+          <t>2026-08-18 00:22:59</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -249,17 +249,17 @@
       </c>
       <c r="M3" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608176588884719</t>
+          <t>4500000320202608183466806505</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="0">
-        <v>49337882</v>
+        <v>49339950</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>王仲槐</t>
+          <t>家和万事兴</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -284,7 +284,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:25</t>
+          <t>2026-08-18 00:04:07</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -314,17 +314,22 @@
       </c>
       <c r="M4" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608171381637652</t>
+          <t>4500000344202608183266732544</t>
+        </is>
+      </c>
+      <c r="N4" s="0" t="inlineStr">
+        <is>
+          <t>亳州</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="0">
-        <v>49337868</v>
+        <v>49339947</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>黄建17373719413</t>
+          <t>温玉明</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -349,7 +354,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:03</t>
+          <t>2026-08-18 00:04:58</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -379,17 +384,17 @@
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608175713808624</t>
+          <t>4500000357202608181657535231</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="0">
-        <v>49337865</v>
+        <v>49339943</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>晓燕</t>
+          <t>春梅</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -414,7 +419,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:01</t>
+          <t>2026-08-18 00:03:49</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -444,17 +449,17 @@
       </c>
       <c r="M6" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608175538967169</t>
+          <t>4500000342202608182239214659</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="0">
-        <v>49337857</v>
+        <v>49339939</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>真心真意</t>
+          <t>青青</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -479,7 +484,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:34:43</t>
+          <t>2026-08-18 00:03:44</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -509,17 +514,17 @@
       </c>
       <c r="M7" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608176387457203</t>
+          <t>4500000355202608185247886970</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="0">
-        <v>49334810</v>
+        <v>49339937</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>candy🧬甘💕</t>
+          <t>开心向日葵🌻</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -544,7 +549,7 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:25:31</t>
+          <t>2026-08-18 00:03:40</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -574,17 +579,17 @@
       </c>
       <c r="M8" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608173665178011</t>
+          <t>4500000319202608184846762524</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="0">
-        <v>49334746</v>
+        <v>49339936</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>雨落弦音</t>
+          <t>彩之缘</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -609,7 +614,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:24:18</t>
+          <t>2026-08-18 00:03:39</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -639,17 +644,17 @@
       </c>
       <c r="M9" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608175925050310</t>
+          <t>4500000342202608186999829929</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="0">
-        <v>49334683</v>
+        <v>49339931</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>🌹六福A413🌹</t>
+          <t>my</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -674,7 +679,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:23:16</t>
+          <t>2026-08-18 00:03:24</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -704,17 +709,17 @@
       </c>
       <c r="M10" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608175320562123</t>
+          <t>4500000383202608186968757749</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="0">
-        <v>49333672</v>
+        <v>49339929</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>☀️知足常乐😊</t>
+          <t>段桂富</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -739,7 +744,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:44</t>
+          <t>2026-08-18 00:04:06</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -769,17 +774,17 @@
       </c>
       <c r="M11" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608178190501918</t>
+          <t>4500000349202608189428147476</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="0">
-        <v>49333665</v>
+        <v>49339923</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>在水一方</t>
+          <t>蓝天</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -804,7 +809,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:41</t>
+          <t>2026-08-18 00:03:07</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -834,17 +839,17 @@
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608175675285016</t>
+          <t>4500000346202608189060114184</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="0">
-        <v>49333658</v>
+        <v>49339921</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>牛牛</t>
+          <t>陌上花开</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -869,7 +874,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:31</t>
+          <t>2026-08-18 00:03:59</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -899,17 +904,17 @@
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608171889470116</t>
+          <t>4500000353202608185881858135</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="0">
-        <v>49333657</v>
+        <v>49339920</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>鲍镇定</t>
+          <t>A红雨伞玲雪养发馆</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -934,7 +939,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:38</t>
+          <t>2026-08-18 00:03:03</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -964,17 +969,17 @@
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608179201028350</t>
+          <t>4500000344202608181810150616</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="0">
-        <v>49333649</v>
+        <v>49339918</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>:-D开心果O:-)</t>
+          <t>胡璎桉</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -999,7 +1004,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:27</t>
+          <t>2026-08-18 00:05:04</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -1029,17 +1034,17 @@
       </c>
       <c r="M15" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608172428227717</t>
+          <t>4500000354202608188854566939</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="0">
-        <v>49333640</v>
+        <v>49337893</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>黛黛</t>
+          <t>郑洁玲</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -1064,7 +1069,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:30</t>
+          <t>2026-08-17 22:36:14</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -1094,17 +1099,17 @@
       </c>
       <c r="M16" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608177275411312</t>
+          <t>4500000340202608171736033078</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="0">
-        <v>49330491</v>
+        <v>49337886</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>兰花草</t>
+          <t>浪漫樱花</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -1129,7 +1134,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:53:31</t>
+          <t>2026-08-17 22:35:44</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -1159,17 +1164,17 @@
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
-          <t>4500000341202608178144232010</t>
+          <t>4500000362202608176588884719</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="0">
-        <v>49330472</v>
+        <v>49337882</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>郝杏月</t>
+          <t>王仲槐</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -1194,7 +1199,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:53:27</t>
+          <t>2026-08-17 22:35:25</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -1224,17 +1229,17 @@
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608176551746821</t>
+          <t>4500000339202608171381637652</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="0">
-        <v>49330471</v>
+        <v>49337868</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>金泽湖水</t>
+          <t>黄建17373719413</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -1259,7 +1264,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:52:46</t>
+          <t>2026-08-17 22:35:03</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
@@ -1289,17 +1294,17 @@
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608175707490842</t>
+          <t>4500000357202608175713808624</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="0">
-        <v>49330470</v>
+        <v>49337865</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>乐惠</t>
+          <t>晓燕</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -1324,7 +1329,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:52:54</t>
+          <t>2026-08-17 22:35:01</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -1354,17 +1359,17 @@
       </c>
       <c r="M20" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608179365238894</t>
+          <t>4500000380202608175538967169</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="0">
-        <v>49302015</v>
+        <v>49337857</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>辰悦</t>
+          <t>真心真意</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -1389,7 +1394,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:22:50</t>
+          <t>2026-08-17 22:34:43</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -1419,17 +1424,17 @@
       </c>
       <c r="M21" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608175953744348</t>
+          <t>4500000362202608176387457203</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="0">
-        <v>49301896</v>
+        <v>49334810</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>简简单单</t>
+          <t>candy🧬甘💕</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -1454,7 +1459,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:05:28</t>
+          <t>2026-08-17 21:25:31</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1484,17 +1489,17 @@
       </c>
       <c r="M22" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608175217008588</t>
+          <t>4500000379202608173665178011</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="0">
-        <v>49301861</v>
+        <v>49334746</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>小优不忘初心</t>
+          <t>雨落弦音</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -1519,7 +1524,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:03</t>
+          <t>2026-08-17 21:24:18</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
@@ -1549,17 +1554,17 @@
       </c>
       <c r="M23" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608176836637946</t>
+          <t>4500000324202608175925050310</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="0">
-        <v>49301860</v>
+        <v>49334683</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>半夏轻浅</t>
+          <t>🌹六福A413🌹</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -1584,7 +1589,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:08</t>
+          <t>2026-08-17 21:23:16</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1614,17 +1619,17 @@
       </c>
       <c r="M24" s="0" t="inlineStr">
         <is>
-          <t>4500000338202608175019525500</t>
+          <t>4500000337202608175320562123</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="0">
-        <v>49301859</v>
+        <v>49333672</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>小璇一（龙树门业</t>
+          <t>☀️知足常乐😊</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -1649,7 +1654,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:52</t>
+          <t>2026-08-17 21:01:44</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1679,17 +1684,17 @@
       </c>
       <c r="M25" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608177884628709</t>
+          <t>4500000380202608178190501918</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="0">
-        <v>49301854</v>
+        <v>49333665</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>铭源霞🔴（养生减肥斑敏痘调理）</t>
+          <t>在水一方</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -1714,7 +1719,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:00</t>
+          <t>2026-08-17 21:01:41</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1744,17 +1749,17 @@
       </c>
       <c r="M26" s="0" t="inlineStr">
         <is>
-          <t>4500000352202608177813577730</t>
+          <t>4500000333202608175675285016</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="0">
-        <v>49301853</v>
+        <v>49333658</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>祥云母婴春姐</t>
+          <t>牛牛</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -1779,7 +1784,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:49</t>
+          <t>2026-08-17 21:01:31</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1809,17 +1814,17 @@
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608178418886316</t>
+          <t>4500000380202608171889470116</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="0">
-        <v>49301852</v>
+        <v>49333657</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>白迎春</t>
+          <t>鲍镇定</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -1844,7 +1849,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:46</t>
+          <t>2026-08-17 21:01:38</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1874,17 +1879,17 @@
       </c>
       <c r="M28" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608174681213879</t>
+          <t>4500000321202608179201028350</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="0">
-        <v>49301850</v>
+        <v>49333649</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>人生靠自己</t>
+          <t>:-D开心果O:-)</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -1909,7 +1914,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:04</t>
+          <t>2026-08-17 21:01:27</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -1939,17 +1944,17 @@
       </c>
       <c r="M29" s="0" t="inlineStr">
         <is>
-          <t>4500000349202608172769831285</t>
+          <t>4500000344202608172428227717</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="0">
-        <v>49301846</v>
+        <v>49333640</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>心静自然凉</t>
+          <t>黛黛</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -1974,7 +1979,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:51</t>
+          <t>2026-08-17 21:01:30</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -2004,17 +2009,17 @@
       </c>
       <c r="M30" s="0" t="inlineStr">
         <is>
-          <t>4500000354202608177412373514</t>
+          <t>4500000316202608177275411312</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="0">
-        <v>49301843</v>
+        <v>49330491</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>ᥬ᭄也用锅贴店💐ᥬ᭄</t>
+          <t>兰花草</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -2039,7 +2044,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:40</t>
+          <t>2026-08-17 19:53:31</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -2069,17 +2074,17 @@
       </c>
       <c r="M31" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608176220568550</t>
+          <t>4500000341202608178144232010</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="0">
-        <v>49300670</v>
+        <v>49330472</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>看透人心，</t>
+          <t>郝杏月</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -2104,7 +2109,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:56:07</t>
+          <t>2026-08-17 19:53:27</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -2134,17 +2139,17 @@
       </c>
       <c r="M32" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608165434325764</t>
+          <t>4500000337202608176551746821</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="0">
-        <v>49300667</v>
+        <v>49330471</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>童心依旧</t>
+          <t>金泽湖水</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -2169,7 +2174,7 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:56:03</t>
+          <t>2026-08-17 19:52:46</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -2199,17 +2204,17 @@
       </c>
       <c r="M33" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608161482824495</t>
+          <t>4500000374202608175707490842</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="0">
-        <v>49300135</v>
+        <v>49330470</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>秋韵</t>
+          <t>乐惠</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -2234,7 +2239,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:34</t>
+          <t>2026-08-17 19:52:54</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
@@ -2264,17 +2269,17 @@
       </c>
       <c r="M34" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608167344457159</t>
+          <t>4500000347202608179365238894</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="0">
-        <v>49300112</v>
+        <v>49302015</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>平安福贵</t>
+          <t>辰悦</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -2299,7 +2304,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:27</t>
+          <t>2026-08-17 00:22:50</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -2329,17 +2334,17 @@
       </c>
       <c r="M35" s="0" t="inlineStr">
         <is>
-          <t>4500000329202608162072183782</t>
+          <t>4500000368202608175953744348</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="0">
-        <v>49300100</v>
+        <v>49301896</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>萱奶奶</t>
+          <t>简简单单</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -2364,7 +2369,7 @@
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:45</t>
+          <t>2026-08-17 00:05:28</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2394,17 +2399,17 @@
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608164279026924</t>
+          <t>4500000353202608175217008588</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="0">
-        <v>49300096</v>
+        <v>49301861</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>泓涧（红健）</t>
+          <t>小优不忘初心</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -2429,7 +2434,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:31</t>
+          <t>2026-08-17 00:04:03</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
@@ -2459,17 +2464,17 @@
       </c>
       <c r="M37" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608161591115326</t>
+          <t>4500000330202608176836637946</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="0">
-        <v>49300095</v>
+        <v>49301860</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>风行云🏇</t>
+          <t>半夏轻浅</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -2494,7 +2499,7 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:13</t>
+          <t>2026-08-17 00:04:08</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2524,17 +2529,17 @@
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608165318502823</t>
+          <t>4500000338202608175019525500</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="0">
-        <v>49300083</v>
+        <v>49301859</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>才秀</t>
+          <t>小璇一（龙树门业</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -2559,7 +2564,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:11</t>
+          <t>2026-08-17 00:03:52</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -2589,22 +2594,17 @@
       </c>
       <c r="M39" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608161669406907</t>
-        </is>
-      </c>
-      <c r="N39" s="0" t="inlineStr">
-        <is>
-          <t>奉贤</t>
+          <t>4500000347202608177884628709</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="0">
-        <v>49300055</v>
+        <v>49301854</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>冰心</t>
+          <t>铭源霞🔴（养生减肥斑敏痘调理）</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:49</t>
+          <t>2026-08-17 00:04:00</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
@@ -2659,17 +2659,17 @@
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608167949730522</t>
+          <t>4500000352202608177813577730</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="0">
-        <v>49300045</v>
+        <v>49301853</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>平</t>
+          <t>祥云母婴春姐</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:20</t>
+          <t>2026-08-17 00:03:49</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
@@ -2724,22 +2724,17 @@
       </c>
       <c r="M41" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608162476754389</t>
-        </is>
-      </c>
-      <c r="N41" s="0" t="inlineStr">
-        <is>
-          <t>荆州</t>
+          <t>4500000337202608178418886316</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="0">
-        <v>49300042</v>
+        <v>49301852</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>赵萍</t>
+          <t>白迎春</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -2764,7 +2759,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:13</t>
+          <t>2026-08-17 00:03:46</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -2794,17 +2789,17 @@
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608168494549151</t>
+          <t>4500000377202608174681213879</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="0">
-        <v>49300034</v>
+        <v>49301850</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>刘华</t>
+          <t>人生靠自己</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -2829,7 +2824,7 @@
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:07</t>
+          <t>2026-08-17 00:04:04</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
@@ -2859,17 +2854,17 @@
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608165458621611</t>
+          <t>4500000349202608172769831285</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="0">
-        <v>49297749</v>
+        <v>49301846</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>沈雨凤</t>
+          <t>心静自然凉</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -2894,7 +2889,7 @@
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:27:24</t>
+          <t>2026-08-17 00:03:51</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
@@ -2924,17 +2919,17 @@
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
-          <t>4500000375202608164415130639</t>
+          <t>4500000354202608177412373514</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="0">
-        <v>49297736</v>
+        <v>49301843</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>莉莉</t>
+          <t>ᥬ᭄也用锅贴店💐ᥬ᭄</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -2959,7 +2954,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:27:09</t>
+          <t>2026-08-17 00:03:40</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
@@ -2989,17 +2984,17 @@
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608163428098661</t>
+          <t>4500000320202608176220568550</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="0">
-        <v>49297681</v>
+        <v>49300670</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>一生平安</t>
+          <t>看透人心，</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -3024,7 +3019,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:25:46</t>
+          <t>2026-08-16 22:56:07</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
@@ -3054,17 +3049,17 @@
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608163491096965</t>
+          <t>4500000365202608165434325764</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="0">
-        <v>49297679</v>
+        <v>49300667</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>孔平</t>
+          <t>童心依旧</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -3089,7 +3084,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:25:57</t>
+          <t>2026-08-16 22:56:03</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
@@ -3119,17 +3114,17 @@
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
-          <t>4500000367202608165709204884</t>
+          <t>4500000369202608161482824495</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="0">
-        <v>49296893</v>
+        <v>49300135</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>逍遥仙子</t>
+          <t>秋韵</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -3154,7 +3149,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:30</t>
+          <t>2026-08-16 22:36:34</t>
         </is>
       </c>
       <c r="H48" s="0" t="inlineStr">
@@ -3184,17 +3179,17 @@
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608167690459739</t>
+          <t>4500000322202608167344457159</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="0">
-        <v>49296884</v>
+        <v>49300112</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>百佳惠大瑞丰药房曹利红</t>
+          <t>平安福贵</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -3219,7 +3214,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:16</t>
+          <t>2026-08-16 22:36:27</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
@@ -3249,17 +3244,17 @@
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
-          <t>4500000332202608162032983613</t>
+          <t>4500000329202608162072183782</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="0">
-        <v>49296874</v>
+        <v>49300100</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>海  角</t>
+          <t>萱奶奶</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -3284,7 +3279,7 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:57</t>
+          <t>2026-08-16 22:35:45</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
@@ -3314,17 +3309,17 @@
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608163623487097</t>
+          <t>4500000345202608164279026924</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="0">
-        <v>49296864</v>
+        <v>49300096</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>曹景玉</t>
+          <t>泓涧（红健）</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -3349,7 +3344,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:45</t>
+          <t>2026-08-16 22:35:31</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
@@ -3379,17 +3374,17 @@
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608163779658463</t>
+          <t>4500000324202608161591115326</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="0">
-        <v>49296863</v>
+        <v>49300095</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>石陆萍</t>
+          <t>风行云🏇</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -3414,7 +3409,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:13</t>
+          <t>2026-08-16 22:36:13</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
@@ -3444,17 +3439,17 @@
       </c>
       <c r="M52" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608161473678444</t>
+          <t>4500000358202608165318502823</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="0">
-        <v>49296849</v>
+        <v>49300083</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>阿荣</t>
+          <t>才秀</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -3479,7 +3474,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:43</t>
+          <t>2026-08-16 22:35:11</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -3509,17 +3504,22 @@
       </c>
       <c r="M53" s="0" t="inlineStr">
         <is>
-          <t>4500000318202608169868333535</t>
+          <t>4500000330202608161669406907</t>
+        </is>
+      </c>
+      <c r="N53" s="0" t="inlineStr">
+        <is>
+          <t>奉贤</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="0">
-        <v>49296823</v>
+        <v>49300055</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>周少丽</t>
+          <t>冰心</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:17</t>
+          <t>2026-08-16 22:34:49</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="M54" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608169179019788</t>
+          <t>4500000317202608167949730522</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="0">
-        <v>49296822</v>
+        <v>49300045</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>雨花石</t>
+          <t>平</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:16</t>
+          <t>2026-08-16 22:34:20</t>
         </is>
       </c>
       <c r="H55" s="0" t="inlineStr">
@@ -3639,17 +3639,22 @@
       </c>
       <c r="M55" s="0" t="inlineStr">
         <is>
-          <t>4500000367202608166345332381</t>
+          <t>4500000353202608162476754389</t>
+        </is>
+      </c>
+      <c r="N55" s="0" t="inlineStr">
+        <is>
+          <t>荆州</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="0">
-        <v>49293860</v>
+        <v>49300042</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>树玲</t>
+          <t>赵萍</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -3674,7 +3679,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 19:55:26</t>
+          <t>2026-08-16 22:34:13</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -3704,17 +3709,17 @@
       </c>
       <c r="M56" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608168589310428</t>
+          <t>4500000346202608168494549151</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="0">
-        <v>49293858</v>
+        <v>49300034</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>芬芳</t>
+          <t>刘华</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -3739,7 +3744,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 19:55:42</t>
+          <t>2026-08-16 22:35:07</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
@@ -3769,17 +3774,17 @@
       </c>
       <c r="M57" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608162910375128</t>
+          <t>4500000333202608165458621611</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="0">
-        <v>49197594</v>
+        <v>49297749</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>李秀燕健康顾问</t>
+          <t>沈雨凤</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:55</t>
+          <t>2026-08-16 21:27:24</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
@@ -3834,17 +3839,17 @@
       </c>
       <c r="M58" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608135550322726</t>
+          <t>4500000375202608164415130639</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="0">
-        <v>49197555</v>
+        <v>49297736</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>FXH*</t>
+          <t>莉莉</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -3869,7 +3874,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:10</t>
+          <t>2026-08-16 21:27:09</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -3899,17 +3904,17 @@
       </c>
       <c r="M59" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608139667116905</t>
+          <t>4500000369202608163428098661</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="0">
-        <v>49197551</v>
+        <v>49297681</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>书英</t>
+          <t>一生平安</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -3934,7 +3939,7 @@
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:09</t>
+          <t>2026-08-16 21:25:46</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
@@ -3964,17 +3969,17 @@
       </c>
       <c r="M60" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608135183726220</t>
+          <t>4500000368202608163491096965</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="0">
-        <v>49197500</v>
+        <v>49297679</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>求智慧</t>
+          <t>孔平</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -3999,7 +4004,7 @@
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:54:20</t>
+          <t>2026-08-16 21:25:57</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
@@ -4029,17 +4034,17 @@
       </c>
       <c r="M61" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608136477567012</t>
+          <t>4500000367202608165709204884</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="0">
-        <v>49196660</v>
+        <v>49296893</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>陈书先</t>
+          <t>逍遥仙子</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -4064,7 +4069,7 @@
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:55</t>
+          <t>2026-08-16 21:04:30</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -4094,17 +4099,17 @@
       </c>
       <c r="M62" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608137513582005</t>
+          <t>4500000316202608167690459739</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="0">
-        <v>49196649</v>
+        <v>49296884</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>chenchen</t>
+          <t>百佳惠大瑞丰药房曹利红</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -4129,7 +4134,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:37</t>
+          <t>2026-08-16 21:04:16</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
@@ -4159,17 +4164,17 @@
       </c>
       <c r="M63" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608131193472561</t>
+          <t>4500000332202608162032983613</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="0">
-        <v>49196616</v>
+        <v>49296874</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>因子</t>
+          <t>海  角</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -4194,7 +4199,7 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:34</t>
+          <t>2026-08-16 21:03:57</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
@@ -4224,17 +4229,17 @@
       </c>
       <c r="M64" s="0" t="inlineStr">
         <is>
-          <t>4500000381202608131084069069</t>
+          <t>4500000369202608163623487097</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="0">
-        <v>49196580</v>
+        <v>49296864</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>包容</t>
+          <t>曹景玉</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -4259,7 +4264,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:49</t>
+          <t>2026-08-16 21:03:45</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
@@ -4289,17 +4294,17 @@
       </c>
       <c r="M65" s="0" t="inlineStr">
         <is>
-          <t>4500000329202608134515206220</t>
+          <t>4500000331202608163779658463</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="0">
-        <v>49196556</v>
+        <v>49296863</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>小芳</t>
+          <t>石陆萍</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -4324,7 +4329,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:00</t>
+          <t>2026-08-16 21:04:13</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -4354,17 +4359,17 @@
       </c>
       <c r="M66" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608131586040016</t>
+          <t>4500000351202608161473678444</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="0">
-        <v>49196547</v>
+        <v>49296849</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>雷宁</t>
+          <t>阿荣</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -4389,7 +4394,7 @@
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:30</t>
+          <t>2026-08-16 21:03:43</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -4419,17 +4424,17 @@
       </c>
       <c r="M67" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608133116145497</t>
+          <t>4500000318202608169868333535</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="0">
-        <v>49196546</v>
+        <v>49296823</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>兰莓</t>
+          <t>周少丽</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -4454,7 +4459,7 @@
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:56:17</t>
+          <t>2026-08-16 21:03:17</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
@@ -4484,17 +4489,17 @@
       </c>
       <c r="M68" s="0" t="inlineStr">
         <is>
-          <t>4500000352202608136989637138</t>
+          <t>4500000315202608169179019788</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="0">
-        <v>49196528</v>
+        <v>49296822</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>赵子睿奶奶</t>
+          <t>雨花石</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -4519,7 +4524,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:22</t>
+          <t>2026-08-16 21:03:16</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
@@ -4549,17 +4554,17 @@
       </c>
       <c r="M69" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608137236789446</t>
+          <t>4500000367202608166345332381</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="0">
-        <v>49196510</v>
+        <v>49293860</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>山岭巨人</t>
+          <t>树玲</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -4584,7 +4589,7 @@
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:22</t>
+          <t>2026-08-16 19:55:26</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
@@ -4614,17 +4619,17 @@
       </c>
       <c r="M70" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608138809307553</t>
+          <t>4500000342202608168589310428</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="0">
-        <v>49196507</v>
+        <v>49293858</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>香字钟培芷</t>
+          <t>芬芳</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -4649,7 +4654,7 @@
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:53</t>
+          <t>2026-08-16 19:55:42</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
@@ -4679,17 +4684,17 @@
       </c>
       <c r="M71" s="0" t="inlineStr">
         <is>
-          <t>4500000370202608133660294135</t>
+          <t>4500000358202608162910375128</t>
         </is>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="0">
-        <v>49196498</v>
+        <v>49197594</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>孟光宗</t>
+          <t>李秀燕健康顾问</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -4714,7 +4719,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:37:14</t>
+          <t>2026-08-13 21:55:55</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
@@ -4744,17 +4749,17 @@
       </c>
       <c r="M72" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608138859211736</t>
+          <t>4500000383202608135550322726</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="0">
-        <v>49196495</v>
+        <v>49197555</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>夏雨晴的妈妈（天发水芹</t>
+          <t>FXH*</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -4779,7 +4784,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:41</t>
+          <t>2026-08-13 21:55:10</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
@@ -4809,22 +4814,17 @@
       </c>
       <c r="M73" s="0" t="inlineStr">
         <is>
-          <t>4500000371202608138873102820</t>
-        </is>
-      </c>
-      <c r="N73" s="0" t="inlineStr">
-        <is>
-          <t>湾仔区</t>
+          <t>4500000376202608139667116905</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="0">
-        <v>49196485</v>
+        <v>49197551</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>法苑文印广告</t>
+          <t>书英</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:06</t>
+          <t>2026-08-13 21:55:09</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
@@ -4879,17 +4879,17 @@
       </c>
       <c r="M74" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608139506557676</t>
+          <t>4500000363202608135183726220</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="0">
-        <v>49196481</v>
+        <v>49197500</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>四季果</t>
+          <t>求智慧</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:08</t>
+          <t>2026-08-13 21:54:20</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
@@ -4944,17 +4944,17 @@
       </c>
       <c r="M75" s="0" t="inlineStr">
         <is>
-          <t>4500000335202608134787426208</t>
+          <t>4500000356202608136477567012</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="0">
-        <v>49196479</v>
+        <v>49196660</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>仇尚妹</t>
+          <t>陈书先</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:43</t>
+          <t>2026-08-13 21:35:55</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
@@ -5009,17 +5009,17 @@
       </c>
       <c r="M76" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608136810799236</t>
+          <t>4500000362202608137513582005</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="0">
-        <v>49196478</v>
+        <v>49196649</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>A古庄店大新手机卖场库琳琳</t>
+          <t>chenchen</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:42</t>
+          <t>2026-08-13 21:35:37</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="M77" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608137311399529</t>
+          <t>4500000360202608131193472561</t>
         </is>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="0">
-        <v>49196473</v>
+        <v>49196616</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>刘玉云机械租赁服务部15905691602</t>
+          <t>因子</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:30</t>
+          <t>2026-08-13 21:35:34</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -5139,17 +5139,17 @@
       </c>
       <c r="M78" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608134297741797</t>
+          <t>4500000381202608131084069069</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="0">
-        <v>49196470</v>
+        <v>49196580</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>众舍康安二手房丽姐</t>
+          <t>包容</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:28</t>
+          <t>2026-08-13 21:34:49</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
@@ -5204,17 +5204,17 @@
       </c>
       <c r="M79" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608137489426707</t>
+          <t>4500000329202608134515206220</t>
         </is>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="0">
-        <v>49196462</v>
+        <v>49196556</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>欢欢</t>
+          <t>小芳</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:31</t>
+          <t>2026-08-13 21:34:00</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -5269,17 +5269,17 @@
       </c>
       <c r="M80" s="0" t="inlineStr">
         <is>
-          <t>4500000382202608136078541008</t>
+          <t>4500000380202608131586040016</t>
         </is>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="0">
-        <v>49196456</v>
+        <v>49196547</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>润花</t>
+          <t>雷宁</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:41</t>
+          <t>2026-08-13 21:34:30</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="M81" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608139285322594</t>
+          <t>4500000368202608133116145497</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="0">
-        <v>49196455</v>
+        <v>49196546</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>风之韵</t>
+          <t>兰莓</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:34</t>
+          <t>2026-08-13 21:56:17</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="M82" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608137054529020</t>
+          <t>4500000352202608136989637138</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="0">
-        <v>49196452</v>
+        <v>49196528</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>开心每一天</t>
+          <t>赵子睿奶奶</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:40</t>
+          <t>2026-08-13 21:33:22</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -5464,22 +5464,17 @@
       </c>
       <c r="M83" s="0" t="inlineStr">
         <is>
-          <t>4500000327202608131603927208</t>
-        </is>
-      </c>
-      <c r="N83" s="0" t="inlineStr">
-        <is>
-          <t>连云港</t>
+          <t>4500000345202608137236789446</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="0">
-        <v>49196449</v>
+        <v>49196510</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>吉乐常伴</t>
+          <t>山岭巨人</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -5504,7 +5499,7 @@
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:23</t>
+          <t>2026-08-13 21:35:22</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
@@ -5534,17 +5529,17 @@
       </c>
       <c r="M84" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608139313739490</t>
+          <t>4500000324202608138809307553</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="0">
-        <v>49196445</v>
+        <v>49196507</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>快乐宝贝</t>
+          <t>香字钟培芷</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -5569,7 +5564,7 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:15</t>
+          <t>2026-08-13 21:32:53</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
@@ -5599,17 +5594,17 @@
       </c>
       <c r="M85" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608133056225424</t>
+          <t>4500000370202608133660294135</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="0">
-        <v>49196441</v>
+        <v>49196498</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>感恩快乐每一天</t>
+          <t>孟光宗</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -5634,7 +5629,7 @@
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:13</t>
+          <t>2026-08-13 21:37:14</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
@@ -5664,17 +5659,17 @@
       </c>
       <c r="M86" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608132236113522</t>
+          <t>4500000363202608138859211736</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="0">
-        <v>49196439</v>
+        <v>49196495</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>翰林世家京墨18240001035</t>
+          <t>夏雨晴的妈妈（天发水芹</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -5699,7 +5694,7 @@
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:18</t>
+          <t>2026-08-13 21:32:41</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
@@ -5729,17 +5724,22 @@
       </c>
       <c r="M87" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608131410776307</t>
+          <t>4500000371202608138873102820</t>
+        </is>
+      </c>
+      <c r="N87" s="0" t="inlineStr">
+        <is>
+          <t>湾仔区</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="0">
-        <v>49196437</v>
+        <v>49196485</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>悦朵宝贝</t>
+          <t>法苑文印广告</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:06</t>
+          <t>2026-08-13 21:33:06</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
@@ -5794,17 +5794,17 @@
       </c>
       <c r="M88" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608135681746747</t>
+          <t>4500000379202608139506557676</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="0">
-        <v>49196435</v>
+        <v>49196481</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>我的幸福</t>
+          <t>四季果</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:23</t>
+          <t>2026-08-13 21:33:08</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
@@ -5859,17 +5859,17 @@
       </c>
       <c r="M89" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608138821842807</t>
+          <t>4500000335202608134787426208</t>
         </is>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="0">
-        <v>49196433</v>
+        <v>49196479</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>程胜英</t>
+          <t>仇尚妹</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:33</t>
+          <t>2026-08-13 21:32:43</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
@@ -5924,17 +5924,17 @@
       </c>
       <c r="M90" s="0" t="inlineStr">
         <is>
-          <t>4500000338202608136558136840</t>
+          <t>4500000374202608136810799236</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="0">
-        <v>49196424</v>
+        <v>49196478</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>甘峰源奶奶</t>
+          <t>A古庄店大新手机卖场库琳琳</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:16</t>
+          <t>2026-08-13 21:32:42</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
@@ -5989,17 +5989,17 @@
       </c>
       <c r="M91" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608139681236972</t>
+          <t>4500000373202608137311399529</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="0">
-        <v>49196412</v>
+        <v>49196473</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>贝贝老妈</t>
+          <t>刘玉云机械租赁服务部15905691602</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:49</t>
+          <t>2026-08-13 21:32:30</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
@@ -6054,17 +6054,17 @@
       </c>
       <c r="M92" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608138627203805</t>
+          <t>4500000315202608134297741797</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="0">
-        <v>49196406</v>
+        <v>49196470</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>过好每一天</t>
+          <t>众舍康安二手房丽姐</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:55</t>
+          <t>2026-08-13 21:32:28</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
@@ -6119,17 +6119,17 @@
       </c>
       <c r="M93" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608139484061741</t>
+          <t>4500000325202608137489426707</t>
         </is>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="0">
-        <v>49196403</v>
+        <v>49196462</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>迪迪</t>
+          <t>欢欢</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:58</t>
+          <t>2026-08-13 21:32:31</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -6184,17 +6184,17 @@
       </c>
       <c r="M94" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608138209731181</t>
+          <t>4500000382202608136078541008</t>
         </is>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="0">
-        <v>49196399</v>
+        <v>49196456</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>境随心转</t>
+          <t>润花</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:47</t>
+          <t>2026-08-13 21:32:41</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -6249,17 +6249,17 @@
       </c>
       <c r="M95" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608138946210876</t>
+          <t>4500000365202608139285322594</t>
         </is>
       </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="0">
-        <v>49196391</v>
+        <v>49196455</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>💖海霞💖</t>
+          <t>风之韵</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:01</t>
+          <t>2026-08-13 21:32:34</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -6314,17 +6314,17 @@
       </c>
       <c r="M96" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608133672869122</t>
+          <t>4500000339202608137054529020</t>
         </is>
       </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="0">
-        <v>49196390</v>
+        <v>49196452</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>翠翠</t>
+          <t>开心每一天</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:38</t>
+          <t>2026-08-13 21:32:40</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -6379,22 +6379,22 @@
       </c>
       <c r="M97" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608139683947334</t>
+          <t>4500000327202608131603927208</t>
         </is>
       </c>
       <c r="N97" s="0" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>连云港</t>
         </is>
       </c>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="0">
-        <v>49196389</v>
+        <v>49196449</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>漫步繁华街</t>
+          <t>吉乐常伴</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:39</t>
+          <t>2026-08-13 21:32:23</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="M98" s="0" t="inlineStr">
         <is>
-          <t>4500000375202608135974835236</t>
+          <t>4500000340202608139313739490</t>
         </is>
       </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="0">
-        <v>49196385</v>
+        <v>49196445</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>平淡人生🌲</t>
+          <t>快乐宝贝</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:35</t>
+          <t>2026-08-13 21:32:15</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
@@ -6514,17 +6514,17 @@
       </c>
       <c r="M99" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608136587117638</t>
+          <t>4500000326202608133056225424</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="0">
-        <v>49196384</v>
+        <v>49196441</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>眼镜灯饰城3楼76号15923959748</t>
+          <t>感恩快乐每一天</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:34</t>
+          <t>2026-08-13 21:32:13</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
@@ -6579,17 +6579,17 @@
       </c>
       <c r="M100" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608139966140440</t>
+          <t>4500000383202608132236113522</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="0">
-        <v>49196383</v>
+        <v>49196439</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>喜枝</t>
+          <t>翰林世家京墨18240001035</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:45</t>
+          <t>2026-08-13 21:32:18</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
@@ -6644,17 +6644,17 @@
       </c>
       <c r="M101" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608138694510811</t>
+          <t>4500000315202608131410776307</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="0">
-        <v>49155446</v>
+        <v>49196437</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>笑口常开</t>
+          <t>悦朵宝贝</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:36:06</t>
+          <t>2026-08-13 21:32:06</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
@@ -6709,17 +6709,17 @@
       </c>
       <c r="M102" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608121856487760</t>
+          <t>4500000343202608135681746747</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="0">
-        <v>49155389</v>
+        <v>49196435</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>奥普郭彦丽13937990394</t>
+          <t>我的幸福</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:44</t>
+          <t>2026-08-13 21:32:23</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
@@ -6774,17 +6774,17 @@
       </c>
       <c r="M103" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608124582542642</t>
+          <t>4500000331202608138821842807</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="0">
-        <v>49155374</v>
+        <v>49196433</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>流星雨文华</t>
+          <t>程胜英</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:26</t>
+          <t>2026-08-13 21:32:33</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
@@ -6839,17 +6839,17 @@
       </c>
       <c r="M104" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608121430434820</t>
+          <t>4500000338202608136558136840</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="0">
-        <v>49155368</v>
+        <v>49196424</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>笑对人生</t>
+          <t>甘峰源奶奶</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:56</t>
+          <t>2026-08-13 21:32:16</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -6904,17 +6904,17 @@
       </c>
       <c r="M105" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608126193240482</t>
+          <t>4500000374202608139681236972</t>
         </is>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="0">
-        <v>49155365</v>
+        <v>49196412</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>秀</t>
+          <t>贝贝老妈</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:41</t>
+          <t>2026-08-13 21:31:49</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -6969,17 +6969,17 @@
       </c>
       <c r="M106" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608121090433848</t>
+          <t>4500000360202608138627203805</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="0">
-        <v>49155364</v>
+        <v>49196406</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>冯衣制版18966913385</t>
+          <t>过好每一天</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:09</t>
+          <t>2026-08-13 21:31:55</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="M107" s="0" t="inlineStr">
         <is>
-          <t>4500000348202608122728123344</t>
+          <t>4500000384202608139484061741</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="0">
-        <v>49155363</v>
+        <v>49196403</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>平安</t>
+          <t>迪迪</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:54</t>
+          <t>2026-08-13 21:31:58</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
@@ -7099,17 +7099,17 @@
       </c>
       <c r="M108" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608128317430099</t>
+          <t>4500000326202608138209731181</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="0">
-        <v>49155361</v>
+        <v>49196399</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>春华秋实</t>
+          <t>境随心转</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:48</t>
+          <t>2026-08-13 21:31:47</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
@@ -7164,17 +7164,17 @@
       </c>
       <c r="M109" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608121174096033</t>
+          <t>4500000380202608138946210876</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="0">
-        <v>49155359</v>
+        <v>49196391</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>春梅。</t>
+          <t>💖海霞💖</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:36</t>
+          <t>2026-08-13 21:32:01</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
@@ -7229,17 +7229,17 @@
       </c>
       <c r="M110" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608123637081551</t>
+          <t>4500000326202608133672869122</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="0">
-        <v>49155344</v>
+        <v>49196390</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>自由人生</t>
+          <t>翠翠</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:25</t>
+          <t>2026-08-13 21:31:38</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
@@ -7294,17 +7294,22 @@
       </c>
       <c r="M111" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608129865186226</t>
+          <t>4500000351202608139683947334</t>
+        </is>
+      </c>
+      <c r="N111" s="0" t="inlineStr">
+        <is>
+          <t>广州</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="0">
-        <v>49155337</v>
+        <v>49196389</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>红红</t>
+          <t>漫步繁华街</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
@@ -7329,7 +7334,7 @@
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:50</t>
+          <t>2026-08-13 21:32:39</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
@@ -7359,17 +7364,17 @@
       </c>
       <c r="M112" s="0" t="inlineStr">
         <is>
-          <t>4500000327202608125530964720</t>
+          <t>4500000375202608135974835236</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="0">
-        <v>49155330</v>
+        <v>49196385</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>徐淑香</t>
+          <t>平淡人生🌲</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
@@ -7394,7 +7399,7 @@
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:20</t>
+          <t>2026-08-13 21:31:35</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
@@ -7424,17 +7429,17 @@
       </c>
       <c r="M113" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608124983971576</t>
+          <t>4500000359202608136587117638</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="0">
-        <v>49155314</v>
+        <v>49196384</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>H叶</t>
+          <t>眼镜灯饰城3楼76号15923959748</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
@@ -7459,7 +7464,7 @@
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:57</t>
+          <t>2026-08-13 21:31:34</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
@@ -7489,17 +7494,17 @@
       </c>
       <c r="M114" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608128162955185</t>
+          <t>4500000333202608139966140440</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="0">
-        <v>49155309</v>
+        <v>49196383</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>A0000刘氏修脚红姐</t>
+          <t>喜枝</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
@@ -7524,7 +7529,7 @@
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:47</t>
+          <t>2026-08-13 21:31:45</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
@@ -7554,17 +7559,17 @@
       </c>
       <c r="M115" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608127176361921</t>
+          <t>4500000333202608138694510811</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="0">
-        <v>49155304</v>
+        <v>49155446</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>万树红</t>
+          <t>笑口常开</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
@@ -7589,7 +7594,7 @@
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:52</t>
+          <t>2026-08-12 21:36:06</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -7619,17 +7624,17 @@
       </c>
       <c r="M116" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608123430987084</t>
+          <t>4500000376202608121856487760</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="0">
-        <v>49155293</v>
+        <v>49155389</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>往事如烟</t>
+          <t>奥普郭彦丽13937990394</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
@@ -7654,7 +7659,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:33</t>
+          <t>2026-08-12 21:35:44</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -7684,17 +7689,17 @@
       </c>
       <c r="M117" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608121388094535</t>
+          <t>4500000324202608124582542642</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="0">
-        <v>49155283</v>
+        <v>49155374</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>雪洁</t>
+          <t>流星雨文华</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -7719,7 +7724,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:27</t>
+          <t>2026-08-12 21:35:26</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -7749,17 +7754,17 @@
       </c>
       <c r="M118" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608125072492429</t>
+          <t>4500000377202608121430434820</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="0">
-        <v>49155274</v>
+        <v>49155368</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>文英</t>
+          <t>笑对人生</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
@@ -7784,7 +7789,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:24</t>
+          <t>2026-08-12 21:34:56</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -7814,17 +7819,17 @@
       </c>
       <c r="M119" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608127495955817</t>
+          <t>4500000316202608126193240482</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="0">
-        <v>49155273</v>
+        <v>49155365</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>宫本江</t>
+          <t>秀</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
@@ -7849,7 +7854,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:34:41</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
@@ -7879,17 +7884,17 @@
       </c>
       <c r="M120" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608122111396208</t>
+          <t>4500000363202608121090433848</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="0">
-        <v>49155272</v>
+        <v>49155364</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>悠闲的人</t>
+          <t>冯衣制版18966913385</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
@@ -7914,7 +7919,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:13</t>
+          <t>2026-08-12 21:35:09</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
@@ -7944,17 +7949,17 @@
       </c>
       <c r="M121" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608122303219210</t>
+          <t>4500000348202608122728123344</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="0">
-        <v>49155271</v>
+        <v>49155363</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>幸福人生</t>
+          <t>平安</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
@@ -7979,7 +7984,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:08</t>
+          <t>2026-08-12 21:34:54</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
@@ -8009,17 +8014,17 @@
       </c>
       <c r="M122" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608124799146350</t>
+          <t>4500000320202608128317430099</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="0">
-        <v>49155270</v>
+        <v>49155361</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>雾里看花</t>
+          <t>春华秋实</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
@@ -8044,7 +8049,7 @@
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:15</t>
+          <t>2026-08-12 21:34:48</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
@@ -8074,17 +8079,17 @@
       </c>
       <c r="M123" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608123995555310</t>
+          <t>4500000346202608121174096033</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="0">
-        <v>49155266</v>
+        <v>49155359</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>清风绕指柔</t>
+          <t>春梅。</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
@@ -8109,7 +8114,7 @@
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:31</t>
+          <t>2026-08-12 21:34:36</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
@@ -8139,17 +8144,17 @@
       </c>
       <c r="M124" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608127946689166</t>
+          <t>4500000374202608123637081551</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="0">
-        <v>49155265</v>
+        <v>49155344</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>心想事成南无阿弥陀佛</t>
+          <t>自由人生</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
@@ -8174,7 +8179,7 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:42</t>
+          <t>2026-08-12 21:34:25</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
@@ -8204,17 +8209,17 @@
       </c>
       <c r="M125" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608126996164764</t>
+          <t>4500000317202608129865186226</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="0">
-        <v>49155264</v>
+        <v>49155337</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>刘凤辉</t>
+          <t>红红</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
@@ -8239,7 +8244,7 @@
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:34:50</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
@@ -8269,17 +8274,17 @@
       </c>
       <c r="M126" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608124680304775</t>
+          <t>4500000327202608125530964720</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="0">
-        <v>49155263</v>
+        <v>49155330</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>朱叶</t>
+          <t>徐淑香</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
@@ -8304,7 +8309,7 @@
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:18</t>
+          <t>2026-08-12 21:34:20</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
@@ -8334,17 +8339,17 @@
       </c>
       <c r="M127" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608124445297817</t>
+          <t>4500000359202608124983971576</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="0">
-        <v>49155253</v>
+        <v>49155314</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>一顺百顺。好运来</t>
+          <t>H叶</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
@@ -8369,7 +8374,7 @@
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:51</t>
+          <t>2026-08-12 21:33:57</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
@@ -8399,17 +8404,17 @@
       </c>
       <c r="M128" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608122909608257</t>
+          <t>4500000322202608128162955185</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="0">
-        <v>49155246</v>
+        <v>49155309</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>陈桂芳</t>
+          <t>A0000刘氏修脚红姐</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -8434,7 +8439,7 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:14</t>
+          <t>2026-08-12 21:33:47</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
@@ -8464,17 +8469,17 @@
       </c>
       <c r="M129" s="0" t="inlineStr">
         <is>
-          <t>4500000378202608126828589764</t>
+          <t>4500000333202608127176361921</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="0">
-        <v>49155234</v>
+        <v>49155304</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>黄仲芬15683592716</t>
+          <t>万树红</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
@@ -8499,7 +8504,7 @@
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:52</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -8529,17 +8534,17 @@
       </c>
       <c r="M130" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608129237945248</t>
+          <t>4500000379202608123430987084</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="0">
-        <v>49155233</v>
+        <v>49155293</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>幸福姐赵会玲</t>
+          <t>往事如烟</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
@@ -8564,7 +8569,7 @@
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:04</t>
+          <t>2026-08-12 21:33:33</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -8594,17 +8599,17 @@
       </c>
       <c r="M131" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608128379976752</t>
+          <t>4500000360202608121388094535</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="0">
-        <v>49155230</v>
+        <v>49155283</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>锦鲤果果</t>
+          <t>雪洁</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -8629,7 +8634,7 @@
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:20</t>
+          <t>2026-08-12 21:33:27</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -8659,17 +8664,17 @@
       </c>
       <c r="M132" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608129199323858</t>
+          <t>4500000369202608125072492429</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="0">
-        <v>49155226</v>
+        <v>49155274</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>戎戎</t>
+          <t>文英</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
@@ -8694,7 +8699,7 @@
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:05</t>
+          <t>2026-08-12 21:33:24</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -8724,17 +8729,17 @@
       </c>
       <c r="M133" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608125827170254</t>
+          <t>4500000373202608127495955817</t>
         </is>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="0">
-        <v>49155220</v>
+        <v>49155273</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>阿玉</t>
+          <t>宫本江</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
@@ -8789,17 +8794,17 @@
       </c>
       <c r="M134" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608129272259118</t>
+          <t>4500000346202608122111396208</t>
         </is>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="0">
-        <v>49155219</v>
+        <v>49155272</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>沉淀、</t>
+          <t>悠闲的人</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
@@ -8824,7 +8829,7 @@
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:13</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -8854,17 +8859,17 @@
       </c>
       <c r="M135" s="0" t="inlineStr">
         <is>
-          <t>4500000372202608124305947387</t>
+          <t>4500000331202608122303219210</t>
         </is>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="0">
-        <v>49155216</v>
+        <v>49155271</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>晴天</t>
+          <t>幸福人生</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
@@ -8889,7 +8894,7 @@
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:07</t>
+          <t>2026-08-12 21:34:08</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -8919,17 +8924,17 @@
       </c>
       <c r="M136" s="0" t="inlineStr">
         <is>
-          <t>4500000334202608122833385690</t>
+          <t>4500000333202608124799146350</t>
         </is>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="0">
-        <v>49155210</v>
+        <v>49155270</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>开正商行</t>
+          <t>雾里看花</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
@@ -8954,7 +8959,7 @@
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:15</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -8984,17 +8989,17 @@
       </c>
       <c r="M137" s="0" t="inlineStr">
         <is>
-          <t>4500000348202608127466098812</t>
+          <t>4500000331202608123995555310</t>
         </is>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="0">
-        <v>49155208</v>
+        <v>49155266</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>傻傻的幸福</t>
+          <t>清风绕指柔</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
@@ -9019,7 +9024,7 @@
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:31</t>
         </is>
       </c>
       <c r="H138" s="0" t="inlineStr">
@@ -9049,17 +9054,17 @@
       </c>
       <c r="M138" s="0" t="inlineStr">
         <is>
-          <t>4500000378202608122593720010</t>
+          <t>4500000333202608127946689166</t>
         </is>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="0">
-        <v>49155205</v>
+        <v>49155265</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>你好</t>
+          <t>心想事成南无阿弥陀佛</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
@@ -9084,7 +9089,7 @@
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:59</t>
+          <t>2026-08-12 21:33:42</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -9114,17 +9119,17 @@
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
-          <t>4500000335202608122478222937</t>
+          <t>4500000330202608126996164764</t>
         </is>
       </c>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="0">
-        <v>49155203</v>
+        <v>49155264</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>一生有你</t>
+          <t>刘凤辉</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
@@ -9149,7 +9154,7 @@
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -9179,17 +9184,17 @@
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608129324316511</t>
+          <t>4500000330202608124680304775</t>
         </is>
       </c>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="0">
-        <v>49155200</v>
+        <v>49155263</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>朱叶</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
@@ -9214,7 +9219,7 @@
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:09</t>
+          <t>2026-08-12 21:33:18</t>
         </is>
       </c>
       <c r="H141" s="0" t="inlineStr">
@@ -9244,17 +9249,17 @@
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608125850014769</t>
+          <t>4500000345202608124445297817</t>
         </is>
       </c>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="0">
-        <v>49155197</v>
+        <v>49155253</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>桂芝改名叫张淑玮</t>
+          <t>一顺百顺。好运来</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
@@ -9279,7 +9284,7 @@
       </c>
       <c r="G142" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:00</t>
+          <t>2026-08-12 21:33:51</t>
         </is>
       </c>
       <c r="H142" s="0" t="inlineStr">
@@ -9309,17 +9314,17 @@
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608121228274851</t>
+          <t>4500000326202608122909608257</t>
         </is>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="0">
-        <v>49155194</v>
+        <v>49155246</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>自强不息</t>
+          <t>陈桂芳</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -9374,17 +9379,17 @@
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608124140031616</t>
+          <t>4500000378202608126828589764</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="0">
-        <v>49155192</v>
+        <v>49155234</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>时光如水</t>
+          <t>黄仲芬15683592716</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -9409,7 +9414,7 @@
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:03</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -9439,17 +9444,17 @@
       </c>
       <c r="M144" s="0" t="inlineStr">
         <is>
-          <t>4500000364202608128865933230</t>
+          <t>4500000325202608129237945248</t>
         </is>
       </c>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="0">
-        <v>49155187</v>
+        <v>49155233</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>幸福姐赵会玲</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
@@ -9474,7 +9479,7 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:34:04</t>
         </is>
       </c>
       <c r="H145" s="0" t="inlineStr">
@@ -9504,17 +9509,17 @@
       </c>
       <c r="M145" s="0" t="inlineStr">
         <is>
-          <t>4500000334202608125275144248</t>
+          <t>4500000317202608128379976752</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="0">
-        <v>49155186</v>
+        <v>49155230</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>星辰</t>
+          <t>锦鲤果果</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
@@ -9539,7 +9544,7 @@
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:52</t>
+          <t>2026-08-12 21:33:20</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -9569,17 +9574,17 @@
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608121378976306</t>
+          <t>4500000322202608129199323858</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="0">
-        <v>49155185</v>
+        <v>49155226</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>天津温室大棚光伏厂家18920981728</t>
+          <t>戎戎</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -9604,7 +9609,7 @@
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:32</t>
+          <t>2026-08-12 21:33:05</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -9634,17 +9639,17 @@
       </c>
       <c r="M147" s="0" t="inlineStr">
         <is>
-          <t>4500000318202608125631581660</t>
+          <t>4500000331202608125827170254</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="0">
-        <v>49155184</v>
+        <v>49155220</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>惠民</t>
+          <t>阿玉</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -9669,7 +9674,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:08</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -9699,17 +9704,17 @@
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
-          <t>4500000355202608121279528970</t>
+          <t>4500000345202608129272259118</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="0">
-        <v>49155180</v>
+        <v>49155219</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>常青树</t>
+          <t>沉淀、</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
@@ -9734,7 +9739,7 @@
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:06</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -9764,17 +9769,17 @@
       </c>
       <c r="M149" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608125426925788</t>
+          <t>4500000372202608124305947387</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="0">
-        <v>49155178</v>
+        <v>49155216</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>玉伟</t>
+          <t>晴天</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -9829,17 +9834,17 @@
       </c>
       <c r="M150" s="0" t="inlineStr">
         <is>
-          <t>4500000364202608125205677586</t>
+          <t>4500000334202608122833385690</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="0">
-        <v>49155171</v>
+        <v>49155210</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>秦晓娟～中医五官排毒</t>
+          <t>开正商行</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
@@ -9894,17 +9899,17 @@
       </c>
       <c r="M151" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608129265074581</t>
+          <t>4500000348202608127466098812</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="0">
-        <v>49155167</v>
+        <v>49155208</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>水琴</t>
+          <t>傻傻的幸福</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
@@ -9959,17 +9964,17 @@
       </c>
       <c r="M152" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608128554791016</t>
+          <t>4500000378202608122593720010</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="0">
-        <v>49155163</v>
+        <v>49155205</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>祥云ಠ_ಠ</t>
+          <t>你好</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -9994,7 +9999,7 @@
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:32:59</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -10024,17 +10029,17 @@
       </c>
       <c r="M153" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608126804876906</t>
+          <t>4500000335202608122478222937</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="0">
-        <v>49155162</v>
+        <v>49155203</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>雪绒花</t>
+          <t>一生有你</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
@@ -10059,7 +10064,7 @@
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:00</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -10089,17 +10094,17 @@
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608122943306781</t>
+          <t>4500000369202608129324316511</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="0">
-        <v>49155161</v>
+        <v>49155200</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>        糖果</t>
+          <t>618</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
@@ -10124,7 +10129,7 @@
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:52</t>
+          <t>2026-08-12 21:33:09</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -10154,17 +10159,17 @@
       </c>
       <c r="M155" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608121712400624</t>
+          <t>4500000384202608125850014769</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="0">
-        <v>49155157</v>
+        <v>49155197</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>流失的岁月</t>
+          <t>桂芝改名叫张淑玮</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -10189,7 +10194,7 @@
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:11</t>
+          <t>2026-08-12 21:33:00</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -10219,17 +10224,17 @@
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608126379751055</t>
+          <t>4500000351202608121228274851</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="0">
-        <v>49155152</v>
+        <v>49155194</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>夏末幽荷</t>
+          <t>自强不息</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
@@ -10254,7 +10259,7 @@
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:33:14</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -10284,17 +10289,17 @@
       </c>
       <c r="M157" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608128669470764</t>
+          <t>4500000356202608124140031616</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="0">
-        <v>49155150</v>
+        <v>49155192</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>药曼</t>
+          <t>时光如水</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
@@ -10319,7 +10324,7 @@
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:33:03</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -10349,17 +10354,17 @@
       </c>
       <c r="M158" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608127294126669</t>
+          <t>4500000364202608128865933230</t>
         </is>
       </c>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="0">
-        <v>49155149</v>
+        <v>49155187</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>🌺 谭谭🌺</t>
+          <t>张丽</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -10384,7 +10389,7 @@
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:58</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -10414,17 +10419,17 @@
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
-          <t>4500000350202608121029117778</t>
+          <t>4500000334202608125275144248</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="0">
-        <v>49155148</v>
+        <v>49155186</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>王玉(邮局对面卖手机)</t>
+          <t>星辰</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
@@ -10449,7 +10454,7 @@
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:52</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -10479,17 +10484,17 @@
       </c>
       <c r="M160" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608126218721690</t>
+          <t>4500000373202608121378976306</t>
         </is>
       </c>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="0">
-        <v>49155147</v>
+        <v>49155185</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>美好夕阳</t>
+          <t>天津温室大棚光伏厂家18920981728</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -10514,7 +10519,7 @@
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:33:32</t>
         </is>
       </c>
       <c r="H161" s="0" t="inlineStr">
@@ -10544,17 +10549,17 @@
       </c>
       <c r="M161" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608128224202725</t>
+          <t>4500000318202608125631581660</t>
         </is>
       </c>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="0">
-        <v>49155145</v>
+        <v>49155184</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>平凡</t>
+          <t>惠民</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -10579,7 +10584,7 @@
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:57</t>
+          <t>2026-08-12 21:33:08</t>
         </is>
       </c>
       <c r="H162" s="0" t="inlineStr">
@@ -10609,17 +10614,17 @@
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608122476247171</t>
+          <t>4500000355202608121279528970</t>
         </is>
       </c>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="0">
-        <v>49155143</v>
+        <v>49155180</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>唐洪</t>
+          <t>常青树</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
@@ -10644,7 +10649,7 @@
       </c>
       <c r="G163" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:45</t>
+          <t>2026-08-12 21:33:06</t>
         </is>
       </c>
       <c r="H163" s="0" t="inlineStr">
@@ -10674,17 +10679,17 @@
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
-          <t>4500000350202608125309483592</t>
+          <t>4500000357202608125426925788</t>
         </is>
       </c>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="0">
-        <v>49155140</v>
+        <v>49155178</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>浅笑</t>
+          <t>玉伟</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
@@ -10709,7 +10714,7 @@
       </c>
       <c r="G164" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:57</t>
+          <t>2026-08-12 21:33:07</t>
         </is>
       </c>
       <c r="H164" s="0" t="inlineStr">
@@ -10739,17 +10744,17 @@
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608123442658613</t>
+          <t>4500000364202608125205677586</t>
         </is>
       </c>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="0">
-        <v>49155137</v>
+        <v>49155171</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>梅放芳香</t>
+          <t>秦晓娟～中医五官排毒</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
@@ -10774,7 +10779,7 @@
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:59</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H165" s="0" t="inlineStr">
@@ -10804,17 +10809,17 @@
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608127843962862</t>
+          <t>4500000365202608129265074581</t>
         </is>
       </c>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="0">
-        <v>49155135</v>
+        <v>49155167</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>吴素华</t>
+          <t>水琴</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
@@ -10839,7 +10844,7 @@
       </c>
       <c r="G166" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H166" s="0" t="inlineStr">
@@ -10869,17 +10874,17 @@
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608124292727044</t>
+          <t>4500000315202608128554791016</t>
         </is>
       </c>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="0">
-        <v>49155132</v>
+        <v>49155163</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>苗斯妤铂金牌月嫂催乳18839028160</t>
+          <t>祥云ಠ_ಠ</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
@@ -10904,7 +10909,7 @@
       </c>
       <c r="G167" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:46</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H167" s="0" t="inlineStr">
@@ -10934,17 +10939,17 @@
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608123141162109</t>
+          <t>4500000344202608126804876906</t>
         </is>
       </c>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="0">
-        <v>49155131</v>
+        <v>49155162</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>瓷星.</t>
+          <t>雪绒花</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
@@ -10969,7 +10974,7 @@
       </c>
       <c r="G168" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:33:00</t>
         </is>
       </c>
       <c r="H168" s="0" t="inlineStr">
@@ -10999,17 +11004,17 @@
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608121548709297</t>
+          <t>4500000343202608122943306781</t>
         </is>
       </c>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="0">
-        <v>49155129</v>
+        <v>49155161</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>妈咪宝贝</t>
+          <t>        糖果</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
@@ -11034,7 +11039,7 @@
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:42</t>
+          <t>2026-08-12 21:32:52</t>
         </is>
       </c>
       <c r="H169" s="0" t="inlineStr">
@@ -11064,17 +11069,17 @@
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608127726342481</t>
+          <t>4500000384202608121712400624</t>
         </is>
       </c>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="0">
-        <v>49155128</v>
+        <v>49155157</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>愿结天下有缘人</t>
+          <t>流失的岁月</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
@@ -11099,7 +11104,7 @@
       </c>
       <c r="G170" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:46</t>
+          <t>2026-08-12 21:33:11</t>
         </is>
       </c>
       <c r="H170" s="0" t="inlineStr">
@@ -11129,17 +11134,17 @@
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608128699617090</t>
+          <t>4500000379202608126379751055</t>
         </is>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="0">
-        <v>49155124</v>
+        <v>49155152</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>勿忘初心</t>
+          <t>夏末幽荷</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
@@ -11194,17 +11199,17 @@
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608128217629837</t>
+          <t>4500000337202608128669470764</t>
         </is>
       </c>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="0">
-        <v>49155123</v>
+        <v>49155150</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>芳草天涯</t>
+          <t>药曼</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
@@ -11229,7 +11234,7 @@
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:32</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H172" s="0" t="inlineStr">
@@ -11259,22 +11264,17 @@
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608123653997556</t>
-        </is>
-      </c>
-      <c r="N172" s="0" t="inlineStr">
-        <is>
-          <t>合肥</t>
+          <t>4500000345202608127294126669</t>
         </is>
       </c>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="0">
-        <v>49155120</v>
+        <v>49155149</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>记忆中的你</t>
+          <t>🌺 谭谭🌺</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:53</t>
+          <t>2026-08-12 21:32:58</t>
         </is>
       </c>
       <c r="H173" s="0" t="inlineStr">
@@ -11329,17 +11329,17 @@
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608124401684219</t>
+          <t>4500000350202608121029117778</t>
         </is>
       </c>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="0">
-        <v>49155114</v>
+        <v>49155148</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>微笑取暖</t>
+          <t>王玉(邮局对面卖手机)</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:38</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H174" s="0" t="inlineStr">
@@ -11394,17 +11394,17 @@
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608121874803628</t>
+          <t>4500000342202608126218721690</t>
         </is>
       </c>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="0">
-        <v>49155112</v>
+        <v>49155147</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>净心李芸</t>
+          <t>美好夕阳</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:33</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H175" s="0" t="inlineStr">
@@ -11459,17 +11459,17 @@
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608126115898528</t>
+          <t>4500000343202608128224202725</t>
         </is>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="0">
-        <v>49155108</v>
+        <v>49155145</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>衡澜</t>
+          <t>平凡</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:32</t>
+          <t>2026-08-12 21:32:57</t>
         </is>
       </c>
       <c r="H176" s="0" t="inlineStr">
@@ -11524,17 +11524,17 @@
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608128833814214</t>
+          <t>4500000359202608122476247171</t>
         </is>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="0">
-        <v>49155098</v>
+        <v>49155143</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>珂</t>
+          <t>唐洪</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:39</t>
+          <t>2026-08-12 21:32:45</t>
         </is>
       </c>
       <c r="H177" s="0" t="inlineStr">
@@ -11589,17 +11589,17 @@
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608128766183266</t>
+          <t>4500000350202608125309483592</t>
         </is>
       </c>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="0">
-        <v>49155095</v>
+        <v>49155140</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>平安保险~王家宝</t>
+          <t>浅笑</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:32:57</t>
         </is>
       </c>
       <c r="H178" s="0" t="inlineStr">
@@ -11654,17 +11654,17 @@
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608129139460754</t>
+          <t>4500000360202608123442658613</t>
         </is>
       </c>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="0">
-        <v>49155092</v>
+        <v>49155137</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>爱情海</t>
+          <t>梅放芳香</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:23</t>
+          <t>2026-08-12 21:32:59</t>
         </is>
       </c>
       <c r="H179" s="0" t="inlineStr">
@@ -11719,17 +11719,17 @@
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608125918396999</t>
+          <t>4500000356202608127843962862</t>
         </is>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="0">
-        <v>49155090</v>
+        <v>49155135</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>三月桃花</t>
+          <t>吴素华</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:26</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H180" s="0" t="inlineStr">
@@ -11784,70 +11784,985 @@
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
-          <t>4500000382202608128744277768</t>
+          <t>4500000339202608124292727044</t>
         </is>
       </c>
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="0">
+        <v>49155132</v>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t>苗斯妤铂金牌月嫂催乳18839028160</t>
+        </is>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D181" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E181" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F181" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G181" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:46</t>
+        </is>
+      </c>
+      <c r="H181" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J181" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K181" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L181" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M181" s="0" t="inlineStr">
+        <is>
+          <t>4500000322202608123141162109</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" spans="1:14">
+      <c r="A182" s="0">
+        <v>49155131</v>
+      </c>
+      <c r="B182" s="0" t="inlineStr">
+        <is>
+          <t>瓷星.</t>
+        </is>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D182" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E182" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F182" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G182" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:50</t>
+        </is>
+      </c>
+      <c r="H182" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J182" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K182" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L182" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M182" s="0" t="inlineStr">
+        <is>
+          <t>4500000383202608121548709297</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" spans="1:14">
+      <c r="A183" s="0">
+        <v>49155129</v>
+      </c>
+      <c r="B183" s="0" t="inlineStr">
+        <is>
+          <t>妈咪宝贝</t>
+        </is>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D183" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E183" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F183" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G183" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:42</t>
+        </is>
+      </c>
+      <c r="H183" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J183" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K183" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L183" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M183" s="0" t="inlineStr">
+        <is>
+          <t>4500000347202608127726342481</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" spans="1:14">
+      <c r="A184" s="0">
+        <v>49155128</v>
+      </c>
+      <c r="B184" s="0" t="inlineStr">
+        <is>
+          <t>愿结天下有缘人</t>
+        </is>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D184" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E184" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F184" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G184" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:46</t>
+        </is>
+      </c>
+      <c r="H184" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J184" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K184" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L184" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M184" s="0" t="inlineStr">
+        <is>
+          <t>4500000321202608128699617090</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" spans="1:14">
+      <c r="A185" s="0">
+        <v>49155124</v>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
+          <t>勿忘初心</t>
+        </is>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D185" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E185" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F185" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G185" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:49</t>
+        </is>
+      </c>
+      <c r="H185" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J185" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K185" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L185" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M185" s="0" t="inlineStr">
+        <is>
+          <t>4500000373202608128217629837</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" spans="1:14">
+      <c r="A186" s="0">
+        <v>49155123</v>
+      </c>
+      <c r="B186" s="0" t="inlineStr">
+        <is>
+          <t>芳草天涯</t>
+        </is>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D186" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E186" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F186" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G186" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:32</t>
+        </is>
+      </c>
+      <c r="H186" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J186" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K186" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L186" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M186" s="0" t="inlineStr">
+        <is>
+          <t>4500000321202608123653997556</t>
+        </is>
+      </c>
+      <c r="N186" s="0" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" spans="1:14">
+      <c r="A187" s="0">
+        <v>49155120</v>
+      </c>
+      <c r="B187" s="0" t="inlineStr">
+        <is>
+          <t>记忆中的你</t>
+        </is>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D187" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E187" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F187" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G187" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:53</t>
+        </is>
+      </c>
+      <c r="H187" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J187" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K187" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L187" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M187" s="0" t="inlineStr">
+        <is>
+          <t>4500000326202608124401684219</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" spans="1:14">
+      <c r="A188" s="0">
+        <v>49155114</v>
+      </c>
+      <c r="B188" s="0" t="inlineStr">
+        <is>
+          <t>微笑取暖</t>
+        </is>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D188" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E188" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F188" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G188" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:33:38</t>
+        </is>
+      </c>
+      <c r="H188" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J188" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K188" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L188" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M188" s="0" t="inlineStr">
+        <is>
+          <t>4500000325202608121874803628</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" spans="1:14">
+      <c r="A189" s="0">
+        <v>49155112</v>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
+        <is>
+          <t>净心李芸</t>
+        </is>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D189" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E189" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F189" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G189" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:33</t>
+        </is>
+      </c>
+      <c r="H189" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J189" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K189" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L189" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M189" s="0" t="inlineStr">
+        <is>
+          <t>4500000351202608126115898528</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" spans="1:14">
+      <c r="A190" s="0">
+        <v>49155108</v>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
+        <is>
+          <t>衡澜</t>
+        </is>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E190" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F190" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G190" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:32</t>
+        </is>
+      </c>
+      <c r="H190" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J190" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K190" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L190" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M190" s="0" t="inlineStr">
+        <is>
+          <t>4500000360202608128833814214</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" spans="1:14">
+      <c r="A191" s="0">
+        <v>49155098</v>
+      </c>
+      <c r="B191" s="0" t="inlineStr">
+        <is>
+          <t>珂</t>
+        </is>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E191" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F191" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G191" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:39</t>
+        </is>
+      </c>
+      <c r="H191" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J191" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K191" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L191" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M191" s="0" t="inlineStr">
+        <is>
+          <t>4500000344202608128766183266</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" spans="1:14">
+      <c r="A192" s="0">
+        <v>49155095</v>
+      </c>
+      <c r="B192" s="0" t="inlineStr">
+        <is>
+          <t>平安保险~王家宝</t>
+        </is>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D192" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E192" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F192" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G192" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:54</t>
+        </is>
+      </c>
+      <c r="H192" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J192" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K192" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L192" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M192" s="0" t="inlineStr">
+        <is>
+          <t>4500000321202608129139460754</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" spans="1:14">
+      <c r="A193" s="0">
+        <v>49155092</v>
+      </c>
+      <c r="B193" s="0" t="inlineStr">
+        <is>
+          <t>爱情海</t>
+        </is>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D193" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E193" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F193" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G193" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:23</t>
+        </is>
+      </c>
+      <c r="H193" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I193" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J193" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K193" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L193" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M193" s="0" t="inlineStr">
+        <is>
+          <t>4500000357202608125918396999</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" spans="1:14">
+      <c r="A194" s="0">
+        <v>49155090</v>
+      </c>
+      <c r="B194" s="0" t="inlineStr">
+        <is>
+          <t>三月桃花</t>
+        </is>
+      </c>
+      <c r="C194" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D194" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E194" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F194" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G194" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:26</t>
+        </is>
+      </c>
+      <c r="H194" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J194" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K194" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L194" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M194" s="0" t="inlineStr">
+        <is>
+          <t>4500000382202608128744277768</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" spans="1:14">
+      <c r="A195" s="0">
         <v>49155088</v>
       </c>
-      <c r="B181" s="0" t="inlineStr">
+      <c r="B195" s="0" t="inlineStr">
         <is>
           <t>绘兰艺术李老师</t>
         </is>
       </c>
-      <c r="C181" s="0" t="inlineStr">
-        <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
-        </is>
-      </c>
-      <c r="D181" s="0" t="inlineStr">
-        <is>
-          <t>训练营</t>
-        </is>
-      </c>
-      <c r="E181" s="0" t="inlineStr">
-        <is>
-          <t>￥1</t>
-        </is>
-      </c>
-      <c r="F181" s="0" t="inlineStr">
-        <is>
-          <t>￥1</t>
-        </is>
-      </c>
-      <c r="G181" s="0" t="inlineStr">
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D195" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E195" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F195" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G195" s="0" t="inlineStr">
         <is>
           <t>2026-08-12 21:32:20</t>
         </is>
       </c>
-      <c r="H181" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I181" s="0" t="inlineStr">
-        <is>
-          <t>彩虹-抖音1元瑜伽</t>
-        </is>
-      </c>
-      <c r="J181" s="0" t="inlineStr">
-        <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
-        </is>
-      </c>
-      <c r="K181" s="0" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="L181" s="0" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="M181" s="0" t="inlineStr">
+      <c r="H195" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J195" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K195" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L195" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M195" s="0" t="inlineStr">
         <is>
           <t>4500000358202608128940402527</t>
         </is>

--- a/data/exports/王颖瑜伽/dist_order_2026-08-18.xlsx
+++ b/data/exports/王颖瑜伽/dist_order_2026-08-18.xlsx
@@ -125,11 +125,11 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="0">
-        <v>49340095</v>
+        <v>49375111</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>小小</t>
+          <t>万事大吉</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -154,7 +154,7 @@
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:24:20</t>
+          <t>2026-08-18 21:05:57</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -184,17 +184,17 @@
       </c>
       <c r="M2" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608185905136033</t>
+          <t>4500000344202608187074952472</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="0">
-        <v>49340080</v>
+        <v>49375081</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>封艳丽</t>
+          <t>如鱼得水</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -219,7 +219,7 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:22:59</t>
+          <t>2026-08-18 21:04:47</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -249,17 +249,17 @@
       </c>
       <c r="M3" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608183466806505</t>
+          <t>4500000369202608189110994857</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="0">
-        <v>49339950</v>
+        <v>49375015</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>家和万事兴</t>
+          <t>母爱</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -284,7 +284,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:07</t>
+          <t>2026-08-18 21:03:52</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -314,22 +314,17 @@
       </c>
       <c r="M4" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608183266732544</t>
-        </is>
-      </c>
-      <c r="N4" s="0" t="inlineStr">
-        <is>
-          <t>亳州</t>
+          <t>4500000365202608186111867199</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="0">
-        <v>49339947</v>
+        <v>49375001</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>温玉明</t>
+          <t>郭正平</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -354,7 +349,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:58</t>
+          <t>2026-08-18 21:03:41</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -384,17 +379,17 @@
       </c>
       <c r="M5" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608181657535231</t>
+          <t>4500000358202608187695923792</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="0">
-        <v>49339943</v>
+        <v>49375000</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>春梅</t>
+          <t>云    朵</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -419,7 +414,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:49</t>
+          <t>2026-08-18 21:03:36</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -449,17 +444,17 @@
       </c>
       <c r="M6" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608182239214659</t>
+          <t>4500000361202608184692846233</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="0">
-        <v>49339939</v>
+        <v>49371969</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>青青</t>
+          <t>豆棋奶奶</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -484,7 +479,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:44</t>
+          <t>2026-08-18 19:53:16</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -514,17 +509,17 @@
       </c>
       <c r="M7" s="0" t="inlineStr">
         <is>
-          <t>4500000355202608185247886970</t>
+          <t>4500000381202608187462400910</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="0">
-        <v>49339937</v>
+        <v>49370049</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>开心向日葵🌻</t>
+          <t>熊金娥</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -549,7 +544,7 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:40</t>
+          <t>2026-08-18 19:34:52</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -579,17 +574,17 @@
       </c>
       <c r="M8" s="0" t="inlineStr">
         <is>
-          <t>4500000319202608184846762524</t>
+          <t>4500000343202608186456472403</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="0">
-        <v>49339936</v>
+        <v>49370024</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>彩之缘</t>
+          <t>宏娇18906639773</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -614,7 +609,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:39</t>
+          <t>2026-08-18 19:34:43</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -644,17 +639,17 @@
       </c>
       <c r="M9" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608186999829929</t>
+          <t>4500000356202608181915925686</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="0">
-        <v>49339931</v>
+        <v>49369533</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>my</t>
+          <t>周周有钱</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -679,7 +674,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:24</t>
+          <t>2026-08-18 19:33:32</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
@@ -709,17 +704,17 @@
       </c>
       <c r="M10" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608186968757749</t>
+          <t>4500000324202608183864211631</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="0">
-        <v>49339929</v>
+        <v>49369376</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>段桂富</t>
+          <t>王兰允</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -744,7 +739,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:04:06</t>
+          <t>2026-08-18 19:33:40</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
@@ -774,17 +769,17 @@
       </c>
       <c r="M11" s="0" t="inlineStr">
         <is>
-          <t>4500000349202608189428147476</t>
+          <t>4500000372202608185572793801</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="0">
-        <v>49339923</v>
+        <v>49369344</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>蓝天</t>
+          <t>陈</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -809,7 +804,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:07</t>
+          <t>2026-08-18 19:33:15</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
@@ -839,17 +834,17 @@
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608189060114184</t>
+          <t>4500000361202608183479278224</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="0">
-        <v>49339921</v>
+        <v>49369203</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>陌上花开</t>
+          <t>静心</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -874,7 +869,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:59</t>
+          <t>2026-08-18 19:32:32</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
@@ -904,17 +899,17 @@
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608185881858135</t>
+          <t>4500000377202608182953367773</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="0">
-        <v>49339920</v>
+        <v>49340095</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>A红雨伞玲雪养发馆</t>
+          <t>小小</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -939,7 +934,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:03:03</t>
+          <t>2026-08-18 00:24:20</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -969,17 +964,17 @@
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608181810150616</t>
+          <t>4500000339202608185905136033</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="0">
-        <v>49339918</v>
+        <v>49340080</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>胡璎桉</t>
+          <t>封艳丽</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -1004,7 +999,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>2026-08-18 00:05:04</t>
+          <t>2026-08-18 00:22:59</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
@@ -1034,17 +1029,17 @@
       </c>
       <c r="M15" s="0" t="inlineStr">
         <is>
-          <t>4500000354202608188854566939</t>
+          <t>4500000320202608183466806505</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="0">
-        <v>49337893</v>
+        <v>49339950</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>郑洁玲</t>
+          <t>家和万事兴</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -1069,7 +1064,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:36:14</t>
+          <t>2026-08-18 00:04:07</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
@@ -1099,17 +1094,22 @@
       </c>
       <c r="M16" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608171736033078</t>
+          <t>4500000344202608183266732544</t>
+        </is>
+      </c>
+      <c r="N16" s="0" t="inlineStr">
+        <is>
+          <t>亳州</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="0">
-        <v>49337886</v>
+        <v>49339947</v>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>浪漫樱花</t>
+          <t>温玉明</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:44</t>
+          <t>2026-08-18 00:04:58</t>
         </is>
       </c>
       <c r="H17" s="0" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608176588884719</t>
+          <t>4500000357202608181657535231</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="0">
-        <v>49337882</v>
+        <v>49339943</v>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>王仲槐</t>
+          <t>春梅</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:25</t>
+          <t>2026-08-18 00:03:49</t>
         </is>
       </c>
       <c r="H18" s="0" t="inlineStr">
@@ -1229,17 +1229,17 @@
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608171381637652</t>
+          <t>4500000342202608182239214659</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="0">
-        <v>49337868</v>
+        <v>49339939</v>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>黄建17373719413</t>
+          <t>青青</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G19" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:03</t>
+          <t>2026-08-18 00:03:44</t>
         </is>
       </c>
       <c r="H19" s="0" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608175713808624</t>
+          <t>4500000355202608185247886970</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="0">
-        <v>49337865</v>
+        <v>49339937</v>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>晓燕</t>
+          <t>开心向日葵🌻</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:35:01</t>
+          <t>2026-08-18 00:03:40</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="M20" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608175538967169</t>
+          <t>4500000319202608184846762524</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="0">
-        <v>49337857</v>
+        <v>49339936</v>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>真心真意</t>
+          <t>彩之缘</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 22:34:43</t>
+          <t>2026-08-18 00:03:39</t>
         </is>
       </c>
       <c r="H21" s="0" t="inlineStr">
@@ -1424,17 +1424,17 @@
       </c>
       <c r="M21" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608176387457203</t>
+          <t>4500000342202608186999829929</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="0">
-        <v>49334810</v>
+        <v>49339931</v>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>candy🧬甘💕</t>
+          <t>my</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:25:31</t>
+          <t>2026-08-18 00:03:24</t>
         </is>
       </c>
       <c r="H22" s="0" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="M22" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608173665178011</t>
+          <t>4500000383202608186968757749</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="0">
-        <v>49334746</v>
+        <v>49339929</v>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>雨落弦音</t>
+          <t>段桂富</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:24:18</t>
+          <t>2026-08-18 00:04:06</t>
         </is>
       </c>
       <c r="H23" s="0" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="M23" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608175925050310</t>
+          <t>4500000349202608189428147476</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="0">
-        <v>49334683</v>
+        <v>49339923</v>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>🌹六福A413🌹</t>
+          <t>蓝天</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:23:16</t>
+          <t>2026-08-18 00:03:07</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1619,17 +1619,17 @@
       </c>
       <c r="M24" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608175320562123</t>
+          <t>4500000346202608189060114184</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="0">
-        <v>49333672</v>
+        <v>49339921</v>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>☀️知足常乐😊</t>
+          <t>陌上花开</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:44</t>
+          <t>2026-08-18 00:03:59</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1684,17 +1684,17 @@
       </c>
       <c r="M25" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608178190501918</t>
+          <t>4500000353202608185881858135</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="0">
-        <v>49333665</v>
+        <v>49339920</v>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>在水一方</t>
+          <t>A红雨伞玲雪养发馆</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:41</t>
+          <t>2026-08-18 00:03:03</t>
         </is>
       </c>
       <c r="H26" s="0" t="inlineStr">
@@ -1749,17 +1749,17 @@
       </c>
       <c r="M26" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608175675285016</t>
+          <t>4500000344202608181810150616</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="0">
-        <v>49333658</v>
+        <v>49339918</v>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>牛牛</t>
+          <t>胡璎桉</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:31</t>
+          <t>2026-08-18 00:05:04</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1814,17 +1814,17 @@
       </c>
       <c r="M27" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608171889470116</t>
+          <t>4500000354202608188854566939</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="0">
-        <v>49333657</v>
+        <v>49337893</v>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>鲍镇定</t>
+          <t>郑洁玲</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:38</t>
+          <t>2026-08-17 22:36:14</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1879,17 +1879,17 @@
       </c>
       <c r="M28" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608179201028350</t>
+          <t>4500000340202608171736033078</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="0">
-        <v>49333649</v>
+        <v>49337886</v>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>:-D开心果O:-)</t>
+          <t>浪漫樱花</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:27</t>
+          <t>2026-08-17 22:35:44</t>
         </is>
       </c>
       <c r="H29" s="0" t="inlineStr">
@@ -1944,17 +1944,17 @@
       </c>
       <c r="M29" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608172428227717</t>
+          <t>4500000362202608176588884719</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="0">
-        <v>49333640</v>
+        <v>49337882</v>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>黛黛</t>
+          <t>王仲槐</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 21:01:30</t>
+          <t>2026-08-17 22:35:25</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -2009,17 +2009,17 @@
       </c>
       <c r="M30" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608177275411312</t>
+          <t>4500000339202608171381637652</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="0">
-        <v>49330491</v>
+        <v>49337868</v>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>兰花草</t>
+          <t>黄建17373719413</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:53:31</t>
+          <t>2026-08-17 22:35:03</t>
         </is>
       </c>
       <c r="H31" s="0" t="inlineStr">
@@ -2074,17 +2074,17 @@
       </c>
       <c r="M31" s="0" t="inlineStr">
         <is>
-          <t>4500000341202608178144232010</t>
+          <t>4500000357202608175713808624</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="0">
-        <v>49330472</v>
+        <v>49337865</v>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>郝杏月</t>
+          <t>晓燕</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:53:27</t>
+          <t>2026-08-17 22:35:01</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -2139,17 +2139,17 @@
       </c>
       <c r="M32" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608176551746821</t>
+          <t>4500000380202608175538967169</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="0">
-        <v>49330471</v>
+        <v>49337857</v>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>金泽湖水</t>
+          <t>真心真意</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:52:46</t>
+          <t>2026-08-17 22:34:43</t>
         </is>
       </c>
       <c r="H33" s="0" t="inlineStr">
@@ -2204,17 +2204,17 @@
       </c>
       <c r="M33" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608175707490842</t>
+          <t>4500000362202608176387457203</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="0">
-        <v>49330470</v>
+        <v>49334810</v>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>乐惠</t>
+          <t>candy🧬甘💕</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 19:52:54</t>
+          <t>2026-08-17 21:25:31</t>
         </is>
       </c>
       <c r="H34" s="0" t="inlineStr">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="M34" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608179365238894</t>
+          <t>4500000379202608173665178011</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="0">
-        <v>49302015</v>
+        <v>49334746</v>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>辰悦</t>
+          <t>雨落弦音</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:22:50</t>
+          <t>2026-08-17 21:24:18</t>
         </is>
       </c>
       <c r="H35" s="0" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="M35" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608175953744348</t>
+          <t>4500000324202608175925050310</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="0">
-        <v>49301896</v>
+        <v>49334683</v>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>简简单单</t>
+          <t>🌹六福A413🌹</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="G36" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:05:28</t>
+          <t>2026-08-17 21:23:16</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2399,17 +2399,17 @@
       </c>
       <c r="M36" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608175217008588</t>
+          <t>4500000337202608175320562123</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="0">
-        <v>49301861</v>
+        <v>49333672</v>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>小优不忘初心</t>
+          <t>☀️知足常乐😊</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:03</t>
+          <t>2026-08-17 21:01:44</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
@@ -2464,17 +2464,17 @@
       </c>
       <c r="M37" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608176836637946</t>
+          <t>4500000380202608178190501918</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="0">
-        <v>49301860</v>
+        <v>49333665</v>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>半夏轻浅</t>
+          <t>在水一方</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:08</t>
+          <t>2026-08-17 21:01:41</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="M38" s="0" t="inlineStr">
         <is>
-          <t>4500000338202608175019525500</t>
+          <t>4500000333202608175675285016</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="0">
-        <v>49301859</v>
+        <v>49333658</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>小璇一（龙树门业</t>
+          <t>牛牛</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:52</t>
+          <t>2026-08-17 21:01:31</t>
         </is>
       </c>
       <c r="H39" s="0" t="inlineStr">
@@ -2594,17 +2594,17 @@
       </c>
       <c r="M39" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608177884628709</t>
+          <t>4500000380202608171889470116</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="0">
-        <v>49301854</v>
+        <v>49333657</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>铭源霞🔴（养生减肥斑敏痘调理）</t>
+          <t>鲍镇定</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:00</t>
+          <t>2026-08-17 21:01:38</t>
         </is>
       </c>
       <c r="H40" s="0" t="inlineStr">
@@ -2659,17 +2659,17 @@
       </c>
       <c r="M40" s="0" t="inlineStr">
         <is>
-          <t>4500000352202608177813577730</t>
+          <t>4500000321202608179201028350</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="0">
-        <v>49301853</v>
+        <v>49333649</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>祥云母婴春姐</t>
+          <t>:-D开心果O:-)</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:49</t>
+          <t>2026-08-17 21:01:27</t>
         </is>
       </c>
       <c r="H41" s="0" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="M41" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608178418886316</t>
+          <t>4500000344202608172428227717</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="0">
-        <v>49301852</v>
+        <v>49333640</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>白迎春</t>
+          <t>黛黛</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:46</t>
+          <t>2026-08-17 21:01:30</t>
         </is>
       </c>
       <c r="H42" s="0" t="inlineStr">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="M42" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608174681213879</t>
+          <t>4500000316202608177275411312</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="0">
-        <v>49301850</v>
+        <v>49330491</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>人生靠自己</t>
+          <t>兰花草</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:04:04</t>
+          <t>2026-08-17 19:53:31</t>
         </is>
       </c>
       <c r="H43" s="0" t="inlineStr">
@@ -2854,17 +2854,17 @@
       </c>
       <c r="M43" s="0" t="inlineStr">
         <is>
-          <t>4500000349202608172769831285</t>
+          <t>4500000341202608178144232010</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="0">
-        <v>49301846</v>
+        <v>49330472</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>心静自然凉</t>
+          <t>郝杏月</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:51</t>
+          <t>2026-08-17 19:53:27</t>
         </is>
       </c>
       <c r="H44" s="0" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="M44" s="0" t="inlineStr">
         <is>
-          <t>4500000354202608177412373514</t>
+          <t>4500000337202608176551746821</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="0">
-        <v>49301843</v>
+        <v>49330471</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>ᥬ᭄也用锅贴店💐ᥬ᭄</t>
+          <t>金泽湖水</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>2026-08-17 00:03:40</t>
+          <t>2026-08-17 19:52:46</t>
         </is>
       </c>
       <c r="H45" s="0" t="inlineStr">
@@ -2984,17 +2984,17 @@
       </c>
       <c r="M45" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608176220568550</t>
+          <t>4500000374202608175707490842</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="0">
-        <v>49300670</v>
+        <v>49330470</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>看透人心，</t>
+          <t>乐惠</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:56:07</t>
+          <t>2026-08-17 19:52:54</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
@@ -3049,17 +3049,17 @@
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608165434325764</t>
+          <t>4500000347202608179365238894</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="0">
-        <v>49300667</v>
+        <v>49302015</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>童心依旧</t>
+          <t>辰悦</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:56:03</t>
+          <t>2026-08-17 00:22:50</t>
         </is>
       </c>
       <c r="H47" s="0" t="inlineStr">
@@ -3114,17 +3114,17 @@
       </c>
       <c r="M47" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608161482824495</t>
+          <t>4500000368202608175953744348</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="0">
-        <v>49300135</v>
+        <v>49301896</v>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>秋韵</t>
+          <t>简简单单</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:34</t>
+          <t>2026-08-17 00:05:28</t>
         </is>
       </c>
       <c r="H48" s="0" t="inlineStr">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="M48" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608167344457159</t>
+          <t>4500000353202608175217008588</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="0">
-        <v>49300112</v>
+        <v>49301861</v>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>平安福贵</t>
+          <t>小优不忘初心</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:27</t>
+          <t>2026-08-17 00:04:03</t>
         </is>
       </c>
       <c r="H49" s="0" t="inlineStr">
@@ -3244,17 +3244,17 @@
       </c>
       <c r="M49" s="0" t="inlineStr">
         <is>
-          <t>4500000329202608162072183782</t>
+          <t>4500000330202608176836637946</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="0">
-        <v>49300100</v>
+        <v>49301860</v>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>萱奶奶</t>
+          <t>半夏轻浅</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:45</t>
+          <t>2026-08-17 00:04:08</t>
         </is>
       </c>
       <c r="H50" s="0" t="inlineStr">
@@ -3309,17 +3309,17 @@
       </c>
       <c r="M50" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608164279026924</t>
+          <t>4500000338202608175019525500</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="0">
-        <v>49300096</v>
+        <v>49301859</v>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>泓涧（红健）</t>
+          <t>小璇一（龙树门业</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:31</t>
+          <t>2026-08-17 00:03:52</t>
         </is>
       </c>
       <c r="H51" s="0" t="inlineStr">
@@ -3374,17 +3374,17 @@
       </c>
       <c r="M51" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608161591115326</t>
+          <t>4500000347202608177884628709</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="0">
-        <v>49300095</v>
+        <v>49301854</v>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>风行云🏇</t>
+          <t>铭源霞🔴（养生减肥斑敏痘调理）</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:13</t>
+          <t>2026-08-17 00:04:00</t>
         </is>
       </c>
       <c r="H52" s="0" t="inlineStr">
@@ -3439,17 +3439,17 @@
       </c>
       <c r="M52" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608165318502823</t>
+          <t>4500000352202608177813577730</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="0">
-        <v>49300083</v>
+        <v>49301853</v>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>才秀</t>
+          <t>祥云母婴春姐</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:11</t>
+          <t>2026-08-17 00:03:49</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -3504,22 +3504,17 @@
       </c>
       <c r="M53" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608161669406907</t>
-        </is>
-      </c>
-      <c r="N53" s="0" t="inlineStr">
-        <is>
-          <t>奉贤</t>
+          <t>4500000337202608178418886316</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="0">
-        <v>49300055</v>
+        <v>49301852</v>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>冰心</t>
+          <t>白迎春</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -3544,7 +3539,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:49</t>
+          <t>2026-08-17 00:03:46</t>
         </is>
       </c>
       <c r="H54" s="0" t="inlineStr">
@@ -3574,17 +3569,17 @@
       </c>
       <c r="M54" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608167949730522</t>
+          <t>4500000377202608174681213879</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="0">
-        <v>49300045</v>
+        <v>49301850</v>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>平</t>
+          <t>人生靠自己</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -3609,7 +3604,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:20</t>
+          <t>2026-08-17 00:04:04</t>
         </is>
       </c>
       <c r="H55" s="0" t="inlineStr">
@@ -3639,22 +3634,17 @@
       </c>
       <c r="M55" s="0" t="inlineStr">
         <is>
-          <t>4500000353202608162476754389</t>
-        </is>
-      </c>
-      <c r="N55" s="0" t="inlineStr">
-        <is>
-          <t>荆州</t>
+          <t>4500000349202608172769831285</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="0">
-        <v>49300042</v>
+        <v>49301846</v>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>赵萍</t>
+          <t>心静自然凉</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -3679,7 +3669,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:34:13</t>
+          <t>2026-08-17 00:03:51</t>
         </is>
       </c>
       <c r="H56" s="0" t="inlineStr">
@@ -3709,17 +3699,17 @@
       </c>
       <c r="M56" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608168494549151</t>
+          <t>4500000354202608177412373514</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="0">
-        <v>49300034</v>
+        <v>49301843</v>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>刘华</t>
+          <t>ᥬ᭄也用锅贴店💐ᥬ᭄</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -3744,7 +3734,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 22:35:07</t>
+          <t>2026-08-17 00:03:40</t>
         </is>
       </c>
       <c r="H57" s="0" t="inlineStr">
@@ -3774,17 +3764,17 @@
       </c>
       <c r="M57" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608165458621611</t>
+          <t>4500000320202608176220568550</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="0">
-        <v>49297749</v>
+        <v>49300670</v>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>沈雨凤</t>
+          <t>看透人心，</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -3809,7 +3799,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:27:24</t>
+          <t>2026-08-16 22:56:07</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
@@ -3839,17 +3829,17 @@
       </c>
       <c r="M58" s="0" t="inlineStr">
         <is>
-          <t>4500000375202608164415130639</t>
+          <t>4500000365202608165434325764</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="0">
-        <v>49297736</v>
+        <v>49300667</v>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>莉莉</t>
+          <t>童心依旧</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -3874,7 +3864,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:27:09</t>
+          <t>2026-08-16 22:56:03</t>
         </is>
       </c>
       <c r="H59" s="0" t="inlineStr">
@@ -3904,17 +3894,17 @@
       </c>
       <c r="M59" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608163428098661</t>
+          <t>4500000369202608161482824495</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="0">
-        <v>49297681</v>
+        <v>49300135</v>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>一生平安</t>
+          <t>秋韵</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -3939,7 +3929,7 @@
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:25:46</t>
+          <t>2026-08-16 22:36:34</t>
         </is>
       </c>
       <c r="H60" s="0" t="inlineStr">
@@ -3969,17 +3959,17 @@
       </c>
       <c r="M60" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608163491096965</t>
+          <t>4500000322202608167344457159</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="0">
-        <v>49297679</v>
+        <v>49300112</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>孔平</t>
+          <t>平安福贵</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -4004,7 +3994,7 @@
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:25:57</t>
+          <t>2026-08-16 22:36:27</t>
         </is>
       </c>
       <c r="H61" s="0" t="inlineStr">
@@ -4034,17 +4024,17 @@
       </c>
       <c r="M61" s="0" t="inlineStr">
         <is>
-          <t>4500000367202608165709204884</t>
+          <t>4500000329202608162072183782</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="0">
-        <v>49296893</v>
+        <v>49300100</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>逍遥仙子</t>
+          <t>萱奶奶</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -4069,7 +4059,7 @@
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:30</t>
+          <t>2026-08-16 22:35:45</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -4099,17 +4089,17 @@
       </c>
       <c r="M62" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608167690459739</t>
+          <t>4500000345202608164279026924</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="0">
-        <v>49296884</v>
+        <v>49300096</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>百佳惠大瑞丰药房曹利红</t>
+          <t>泓涧（红健）</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -4134,7 +4124,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:16</t>
+          <t>2026-08-16 22:35:31</t>
         </is>
       </c>
       <c r="H63" s="0" t="inlineStr">
@@ -4164,17 +4154,17 @@
       </c>
       <c r="M63" s="0" t="inlineStr">
         <is>
-          <t>4500000332202608162032983613</t>
+          <t>4500000324202608161591115326</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="0">
-        <v>49296874</v>
+        <v>49300095</v>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>海  角</t>
+          <t>风行云🏇</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -4199,7 +4189,7 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:57</t>
+          <t>2026-08-16 22:36:13</t>
         </is>
       </c>
       <c r="H64" s="0" t="inlineStr">
@@ -4229,17 +4219,17 @@
       </c>
       <c r="M64" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608163623487097</t>
+          <t>4500000358202608165318502823</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="0">
-        <v>49296864</v>
+        <v>49300083</v>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>曹景玉</t>
+          <t>才秀</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -4264,7 +4254,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:45</t>
+          <t>2026-08-16 22:35:11</t>
         </is>
       </c>
       <c r="H65" s="0" t="inlineStr">
@@ -4294,17 +4284,22 @@
       </c>
       <c r="M65" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608163779658463</t>
+          <t>4500000330202608161669406907</t>
+        </is>
+      </c>
+      <c r="N65" s="0" t="inlineStr">
+        <is>
+          <t>奉贤</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="0">
-        <v>49296863</v>
+        <v>49300055</v>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>石陆萍</t>
+          <t>冰心</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -4329,7 +4324,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:04:13</t>
+          <t>2026-08-16 22:34:49</t>
         </is>
       </c>
       <c r="H66" s="0" t="inlineStr">
@@ -4359,17 +4354,17 @@
       </c>
       <c r="M66" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608161473678444</t>
+          <t>4500000317202608167949730522</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="0">
-        <v>49296849</v>
+        <v>49300045</v>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>阿荣</t>
+          <t>平</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -4394,7 +4389,7 @@
       </c>
       <c r="G67" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:43</t>
+          <t>2026-08-16 22:34:20</t>
         </is>
       </c>
       <c r="H67" s="0" t="inlineStr">
@@ -4424,17 +4419,22 @@
       </c>
       <c r="M67" s="0" t="inlineStr">
         <is>
-          <t>4500000318202608169868333535</t>
+          <t>4500000353202608162476754389</t>
+        </is>
+      </c>
+      <c r="N67" s="0" t="inlineStr">
+        <is>
+          <t>荆州</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="0">
-        <v>49296823</v>
+        <v>49300042</v>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>周少丽</t>
+          <t>赵萍</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:17</t>
+          <t>2026-08-16 22:34:13</t>
         </is>
       </c>
       <c r="H68" s="0" t="inlineStr">
@@ -4489,17 +4489,17 @@
       </c>
       <c r="M68" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608169179019788</t>
+          <t>4500000346202608168494549151</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="0">
-        <v>49296822</v>
+        <v>49300034</v>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>雨花石</t>
+          <t>刘华</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 21:03:16</t>
+          <t>2026-08-16 22:35:07</t>
         </is>
       </c>
       <c r="H69" s="0" t="inlineStr">
@@ -4554,17 +4554,17 @@
       </c>
       <c r="M69" s="0" t="inlineStr">
         <is>
-          <t>4500000367202608166345332381</t>
+          <t>4500000333202608165458621611</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="0">
-        <v>49293860</v>
+        <v>49297749</v>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>树玲</t>
+          <t>沈雨凤</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 19:55:26</t>
+          <t>2026-08-16 21:27:24</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
@@ -4619,17 +4619,17 @@
       </c>
       <c r="M70" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608168589310428</t>
+          <t>4500000375202608164415130639</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="0">
-        <v>49293858</v>
+        <v>49297736</v>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>芬芳</t>
+          <t>莉莉</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>2026-08-16 19:55:42</t>
+          <t>2026-08-16 21:27:09</t>
         </is>
       </c>
       <c r="H71" s="0" t="inlineStr">
@@ -4684,17 +4684,17 @@
       </c>
       <c r="M71" s="0" t="inlineStr">
         <is>
-          <t>4500000358202608162910375128</t>
+          <t>4500000369202608163428098661</t>
         </is>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="0">
-        <v>49197594</v>
+        <v>49297681</v>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>李秀燕健康顾问</t>
+          <t>一生平安</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:55</t>
+          <t>2026-08-16 21:25:46</t>
         </is>
       </c>
       <c r="H72" s="0" t="inlineStr">
@@ -4749,17 +4749,17 @@
       </c>
       <c r="M72" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608135550322726</t>
+          <t>4500000368202608163491096965</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="0">
-        <v>49197555</v>
+        <v>49297679</v>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>FXH*</t>
+          <t>孔平</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:10</t>
+          <t>2026-08-16 21:25:57</t>
         </is>
       </c>
       <c r="H73" s="0" t="inlineStr">
@@ -4814,17 +4814,17 @@
       </c>
       <c r="M73" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608139667116905</t>
+          <t>4500000367202608165709204884</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="0">
-        <v>49197551</v>
+        <v>49296893</v>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>书英</t>
+          <t>逍遥仙子</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:55:09</t>
+          <t>2026-08-16 21:04:30</t>
         </is>
       </c>
       <c r="H74" s="0" t="inlineStr">
@@ -4879,17 +4879,17 @@
       </c>
       <c r="M74" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608135183726220</t>
+          <t>4500000316202608167690459739</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="0">
-        <v>49197500</v>
+        <v>49296884</v>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>求智慧</t>
+          <t>百佳惠大瑞丰药房曹利红</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:54:20</t>
+          <t>2026-08-16 21:04:16</t>
         </is>
       </c>
       <c r="H75" s="0" t="inlineStr">
@@ -4944,17 +4944,17 @@
       </c>
       <c r="M75" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608136477567012</t>
+          <t>4500000332202608162032983613</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="0">
-        <v>49196660</v>
+        <v>49296874</v>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>陈书先</t>
+          <t>海  角</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:55</t>
+          <t>2026-08-16 21:03:57</t>
         </is>
       </c>
       <c r="H76" s="0" t="inlineStr">
@@ -5009,17 +5009,17 @@
       </c>
       <c r="M76" s="0" t="inlineStr">
         <is>
-          <t>4500000362202608137513582005</t>
+          <t>4500000369202608163623487097</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="0">
-        <v>49196649</v>
+        <v>49296864</v>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>chenchen</t>
+          <t>曹景玉</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:37</t>
+          <t>2026-08-16 21:03:45</t>
         </is>
       </c>
       <c r="H77" s="0" t="inlineStr">
@@ -5074,17 +5074,17 @@
       </c>
       <c r="M77" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608131193472561</t>
+          <t>4500000331202608163779658463</t>
         </is>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="0">
-        <v>49196616</v>
+        <v>49296863</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>因子</t>
+          <t>石陆萍</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:34</t>
+          <t>2026-08-16 21:04:13</t>
         </is>
       </c>
       <c r="H78" s="0" t="inlineStr">
@@ -5139,17 +5139,17 @@
       </c>
       <c r="M78" s="0" t="inlineStr">
         <is>
-          <t>4500000381202608131084069069</t>
+          <t>4500000351202608161473678444</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="0">
-        <v>49196580</v>
+        <v>49296849</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>包容</t>
+          <t>阿荣</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="G79" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:49</t>
+          <t>2026-08-16 21:03:43</t>
         </is>
       </c>
       <c r="H79" s="0" t="inlineStr">
@@ -5204,17 +5204,17 @@
       </c>
       <c r="M79" s="0" t="inlineStr">
         <is>
-          <t>4500000329202608134515206220</t>
+          <t>4500000318202608169868333535</t>
         </is>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="0">
-        <v>49196556</v>
+        <v>49296823</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>小芳</t>
+          <t>周少丽</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="G80" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:00</t>
+          <t>2026-08-16 21:03:17</t>
         </is>
       </c>
       <c r="H80" s="0" t="inlineStr">
@@ -5269,17 +5269,17 @@
       </c>
       <c r="M80" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608131586040016</t>
+          <t>4500000315202608169179019788</t>
         </is>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="0">
-        <v>49196547</v>
+        <v>49296822</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>雷宁</t>
+          <t>雨花石</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="G81" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:34:30</t>
+          <t>2026-08-16 21:03:16</t>
         </is>
       </c>
       <c r="H81" s="0" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="M81" s="0" t="inlineStr">
         <is>
-          <t>4500000368202608133116145497</t>
+          <t>4500000367202608166345332381</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="0">
-        <v>49196546</v>
+        <v>49293860</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>兰莓</t>
+          <t>树玲</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:56:17</t>
+          <t>2026-08-16 19:55:26</t>
         </is>
       </c>
       <c r="H82" s="0" t="inlineStr">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="M82" s="0" t="inlineStr">
         <is>
-          <t>4500000352202608136989637138</t>
+          <t>4500000342202608168589310428</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="0">
-        <v>49196528</v>
+        <v>49293858</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>赵子睿奶奶</t>
+          <t>芬芳</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="G83" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:22</t>
+          <t>2026-08-16 19:55:42</t>
         </is>
       </c>
       <c r="H83" s="0" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="M83" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608137236789446</t>
+          <t>4500000358202608162910375128</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="0">
-        <v>49196510</v>
+        <v>49197594</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>山岭巨人</t>
+          <t>李秀燕健康顾问</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G84" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:35:22</t>
+          <t>2026-08-13 21:55:55</t>
         </is>
       </c>
       <c r="H84" s="0" t="inlineStr">
@@ -5529,17 +5529,17 @@
       </c>
       <c r="M84" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608138809307553</t>
+          <t>4500000383202608135550322726</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="0">
-        <v>49196507</v>
+        <v>49197555</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>香字钟培芷</t>
+          <t>FXH*</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G85" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:53</t>
+          <t>2026-08-13 21:55:10</t>
         </is>
       </c>
       <c r="H85" s="0" t="inlineStr">
@@ -5594,17 +5594,17 @@
       </c>
       <c r="M85" s="0" t="inlineStr">
         <is>
-          <t>4500000370202608133660294135</t>
+          <t>4500000376202608139667116905</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="0">
-        <v>49196498</v>
+        <v>49197551</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>孟光宗</t>
+          <t>书英</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:37:14</t>
+          <t>2026-08-13 21:55:09</t>
         </is>
       </c>
       <c r="H86" s="0" t="inlineStr">
@@ -5659,17 +5659,17 @@
       </c>
       <c r="M86" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608138859211736</t>
+          <t>4500000363202608135183726220</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="0">
-        <v>49196495</v>
+        <v>49197500</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>夏雨晴的妈妈（天发水芹</t>
+          <t>求智慧</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:41</t>
+          <t>2026-08-13 21:54:20</t>
         </is>
       </c>
       <c r="H87" s="0" t="inlineStr">
@@ -5724,22 +5724,17 @@
       </c>
       <c r="M87" s="0" t="inlineStr">
         <is>
-          <t>4500000371202608138873102820</t>
-        </is>
-      </c>
-      <c r="N87" s="0" t="inlineStr">
-        <is>
-          <t>湾仔区</t>
+          <t>4500000356202608136477567012</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="0">
-        <v>49196485</v>
+        <v>49196660</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>法苑文印广告</t>
+          <t>陈书先</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -5764,7 +5759,7 @@
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:06</t>
+          <t>2026-08-13 21:35:55</t>
         </is>
       </c>
       <c r="H88" s="0" t="inlineStr">
@@ -5794,17 +5789,17 @@
       </c>
       <c r="M88" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608139506557676</t>
+          <t>4500000362202608137513582005</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="0">
-        <v>49196481</v>
+        <v>49196649</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>四季果</t>
+          <t>chenchen</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -5829,7 +5824,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:33:08</t>
+          <t>2026-08-13 21:35:37</t>
         </is>
       </c>
       <c r="H89" s="0" t="inlineStr">
@@ -5859,17 +5854,17 @@
       </c>
       <c r="M89" s="0" t="inlineStr">
         <is>
-          <t>4500000335202608134787426208</t>
+          <t>4500000360202608131193472561</t>
         </is>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="0">
-        <v>49196479</v>
+        <v>49196616</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>仇尚妹</t>
+          <t>因子</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
@@ -5894,7 +5889,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:43</t>
+          <t>2026-08-13 21:35:34</t>
         </is>
       </c>
       <c r="H90" s="0" t="inlineStr">
@@ -5924,17 +5919,17 @@
       </c>
       <c r="M90" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608136810799236</t>
+          <t>4500000381202608131084069069</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="0">
-        <v>49196478</v>
+        <v>49196580</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>A古庄店大新手机卖场库琳琳</t>
+          <t>包容</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
@@ -5959,7 +5954,7 @@
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:42</t>
+          <t>2026-08-13 21:34:49</t>
         </is>
       </c>
       <c r="H91" s="0" t="inlineStr">
@@ -5989,17 +5984,17 @@
       </c>
       <c r="M91" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608137311399529</t>
+          <t>4500000329202608134515206220</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="0">
-        <v>49196473</v>
+        <v>49196556</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>刘玉云机械租赁服务部15905691602</t>
+          <t>小芳</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
@@ -6024,7 +6019,7 @@
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:30</t>
+          <t>2026-08-13 21:34:00</t>
         </is>
       </c>
       <c r="H92" s="0" t="inlineStr">
@@ -6054,17 +6049,17 @@
       </c>
       <c r="M92" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608134297741797</t>
+          <t>4500000380202608131586040016</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="0">
-        <v>49196470</v>
+        <v>49196547</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>众舍康安二手房丽姐</t>
+          <t>雷宁</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
@@ -6089,7 +6084,7 @@
       </c>
       <c r="G93" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:28</t>
+          <t>2026-08-13 21:34:30</t>
         </is>
       </c>
       <c r="H93" s="0" t="inlineStr">
@@ -6119,17 +6114,17 @@
       </c>
       <c r="M93" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608137489426707</t>
+          <t>4500000368202608133116145497</t>
         </is>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="0">
-        <v>49196462</v>
+        <v>49196546</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>欢欢</t>
+          <t>兰莓</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -6154,7 +6149,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:31</t>
+          <t>2026-08-13 21:56:17</t>
         </is>
       </c>
       <c r="H94" s="0" t="inlineStr">
@@ -6184,17 +6179,17 @@
       </c>
       <c r="M94" s="0" t="inlineStr">
         <is>
-          <t>4500000382202608136078541008</t>
+          <t>4500000352202608136989637138</t>
         </is>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="0">
-        <v>49196456</v>
+        <v>49196528</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>润花</t>
+          <t>赵子睿奶奶</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
@@ -6219,7 +6214,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:41</t>
+          <t>2026-08-13 21:33:22</t>
         </is>
       </c>
       <c r="H95" s="0" t="inlineStr">
@@ -6249,17 +6244,17 @@
       </c>
       <c r="M95" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608139285322594</t>
+          <t>4500000345202608137236789446</t>
         </is>
       </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="0">
-        <v>49196455</v>
+        <v>49196510</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>风之韵</t>
+          <t>山岭巨人</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -6284,7 +6279,7 @@
       </c>
       <c r="G96" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:34</t>
+          <t>2026-08-13 21:35:22</t>
         </is>
       </c>
       <c r="H96" s="0" t="inlineStr">
@@ -6314,17 +6309,17 @@
       </c>
       <c r="M96" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608137054529020</t>
+          <t>4500000324202608138809307553</t>
         </is>
       </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="0">
-        <v>49196452</v>
+        <v>49196507</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>开心每一天</t>
+          <t>香字钟培芷</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
@@ -6349,7 +6344,7 @@
       </c>
       <c r="G97" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:40</t>
+          <t>2026-08-13 21:32:53</t>
         </is>
       </c>
       <c r="H97" s="0" t="inlineStr">
@@ -6379,22 +6374,17 @@
       </c>
       <c r="M97" s="0" t="inlineStr">
         <is>
-          <t>4500000327202608131603927208</t>
-        </is>
-      </c>
-      <c r="N97" s="0" t="inlineStr">
-        <is>
-          <t>连云港</t>
+          <t>4500000370202608133660294135</t>
         </is>
       </c>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="0">
-        <v>49196449</v>
+        <v>49196498</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>吉乐常伴</t>
+          <t>孟光宗</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
@@ -6419,7 +6409,7 @@
       </c>
       <c r="G98" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:23</t>
+          <t>2026-08-13 21:37:14</t>
         </is>
       </c>
       <c r="H98" s="0" t="inlineStr">
@@ -6449,17 +6439,17 @@
       </c>
       <c r="M98" s="0" t="inlineStr">
         <is>
-          <t>4500000340202608139313739490</t>
+          <t>4500000363202608138859211736</t>
         </is>
       </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="0">
-        <v>49196445</v>
+        <v>49196495</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>快乐宝贝</t>
+          <t>夏雨晴的妈妈（天发水芹</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
@@ -6484,7 +6474,7 @@
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:15</t>
+          <t>2026-08-13 21:32:41</t>
         </is>
       </c>
       <c r="H99" s="0" t="inlineStr">
@@ -6514,17 +6504,22 @@
       </c>
       <c r="M99" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608133056225424</t>
+          <t>4500000371202608138873102820</t>
+        </is>
+      </c>
+      <c r="N99" s="0" t="inlineStr">
+        <is>
+          <t>湾仔区</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="0">
-        <v>49196441</v>
+        <v>49196485</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>感恩快乐每一天</t>
+          <t>法苑文印广告</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -6549,7 +6544,7 @@
       </c>
       <c r="G100" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:13</t>
+          <t>2026-08-13 21:33:06</t>
         </is>
       </c>
       <c r="H100" s="0" t="inlineStr">
@@ -6579,17 +6574,17 @@
       </c>
       <c r="M100" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608132236113522</t>
+          <t>4500000379202608139506557676</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="0">
-        <v>49196439</v>
+        <v>49196481</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>翰林世家京墨18240001035</t>
+          <t>四季果</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
@@ -6614,7 +6609,7 @@
       </c>
       <c r="G101" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:18</t>
+          <t>2026-08-13 21:33:08</t>
         </is>
       </c>
       <c r="H101" s="0" t="inlineStr">
@@ -6644,17 +6639,17 @@
       </c>
       <c r="M101" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608131410776307</t>
+          <t>4500000335202608134787426208</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="0">
-        <v>49196437</v>
+        <v>49196479</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>悦朵宝贝</t>
+          <t>仇尚妹</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
@@ -6679,7 +6674,7 @@
       </c>
       <c r="G102" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:06</t>
+          <t>2026-08-13 21:32:43</t>
         </is>
       </c>
       <c r="H102" s="0" t="inlineStr">
@@ -6709,17 +6704,17 @@
       </c>
       <c r="M102" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608135681746747</t>
+          <t>4500000374202608136810799236</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="0">
-        <v>49196435</v>
+        <v>49196478</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>我的幸福</t>
+          <t>A古庄店大新手机卖场库琳琳</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
@@ -6744,7 +6739,7 @@
       </c>
       <c r="G103" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:23</t>
+          <t>2026-08-13 21:32:42</t>
         </is>
       </c>
       <c r="H103" s="0" t="inlineStr">
@@ -6774,17 +6769,17 @@
       </c>
       <c r="M103" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608138821842807</t>
+          <t>4500000373202608137311399529</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="0">
-        <v>49196433</v>
+        <v>49196473</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>程胜英</t>
+          <t>刘玉云机械租赁服务部15905691602</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
@@ -6809,7 +6804,7 @@
       </c>
       <c r="G104" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:33</t>
+          <t>2026-08-13 21:32:30</t>
         </is>
       </c>
       <c r="H104" s="0" t="inlineStr">
@@ -6839,17 +6834,17 @@
       </c>
       <c r="M104" s="0" t="inlineStr">
         <is>
-          <t>4500000338202608136558136840</t>
+          <t>4500000315202608134297741797</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="0">
-        <v>49196424</v>
+        <v>49196470</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>甘峰源奶奶</t>
+          <t>众舍康安二手房丽姐</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -6874,7 +6869,7 @@
       </c>
       <c r="G105" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:16</t>
+          <t>2026-08-13 21:32:28</t>
         </is>
       </c>
       <c r="H105" s="0" t="inlineStr">
@@ -6904,17 +6899,17 @@
       </c>
       <c r="M105" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608139681236972</t>
+          <t>4500000325202608137489426707</t>
         </is>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" s="0">
-        <v>49196412</v>
+        <v>49196462</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>贝贝老妈</t>
+          <t>欢欢</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
@@ -6939,7 +6934,7 @@
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:49</t>
+          <t>2026-08-13 21:32:31</t>
         </is>
       </c>
       <c r="H106" s="0" t="inlineStr">
@@ -6969,17 +6964,17 @@
       </c>
       <c r="M106" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608138627203805</t>
+          <t>4500000382202608136078541008</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" s="0">
-        <v>49196406</v>
+        <v>49196456</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>过好每一天</t>
+          <t>润花</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
@@ -7004,7 +6999,7 @@
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:55</t>
+          <t>2026-08-13 21:32:41</t>
         </is>
       </c>
       <c r="H107" s="0" t="inlineStr">
@@ -7034,17 +7029,17 @@
       </c>
       <c r="M107" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608139484061741</t>
+          <t>4500000365202608139285322594</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:14">
       <c r="A108" s="0">
-        <v>49196403</v>
+        <v>49196455</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>迪迪</t>
+          <t>风之韵</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
@@ -7069,7 +7064,7 @@
       </c>
       <c r="G108" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:58</t>
+          <t>2026-08-13 21:32:34</t>
         </is>
       </c>
       <c r="H108" s="0" t="inlineStr">
@@ -7099,17 +7094,17 @@
       </c>
       <c r="M108" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608138209731181</t>
+          <t>4500000339202608137054529020</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="0">
-        <v>49196399</v>
+        <v>49196452</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>境随心转</t>
+          <t>开心每一天</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -7134,7 +7129,7 @@
       </c>
       <c r="G109" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:47</t>
+          <t>2026-08-13 21:32:40</t>
         </is>
       </c>
       <c r="H109" s="0" t="inlineStr">
@@ -7164,17 +7159,22 @@
       </c>
       <c r="M109" s="0" t="inlineStr">
         <is>
-          <t>4500000380202608138946210876</t>
+          <t>4500000327202608131603927208</t>
+        </is>
+      </c>
+      <c r="N109" s="0" t="inlineStr">
+        <is>
+          <t>连云港</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" s="0">
-        <v>49196391</v>
+        <v>49196449</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>💖海霞💖</t>
+          <t>吉乐常伴</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="G110" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:01</t>
+          <t>2026-08-13 21:32:23</t>
         </is>
       </c>
       <c r="H110" s="0" t="inlineStr">
@@ -7229,17 +7229,17 @@
       </c>
       <c r="M110" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608133672869122</t>
+          <t>4500000340202608139313739490</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" s="0">
-        <v>49196390</v>
+        <v>49196445</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>翠翠</t>
+          <t>快乐宝贝</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="G111" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:38</t>
+          <t>2026-08-13 21:32:15</t>
         </is>
       </c>
       <c r="H111" s="0" t="inlineStr">
@@ -7294,22 +7294,17 @@
       </c>
       <c r="M111" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608139683947334</t>
-        </is>
-      </c>
-      <c r="N111" s="0" t="inlineStr">
-        <is>
-          <t>广州</t>
+          <t>4500000326202608133056225424</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" s="0">
-        <v>49196389</v>
+        <v>49196441</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>漫步繁华街</t>
+          <t>感恩快乐每一天</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
@@ -7334,7 +7329,7 @@
       </c>
       <c r="G112" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:32:39</t>
+          <t>2026-08-13 21:32:13</t>
         </is>
       </c>
       <c r="H112" s="0" t="inlineStr">
@@ -7364,17 +7359,17 @@
       </c>
       <c r="M112" s="0" t="inlineStr">
         <is>
-          <t>4500000375202608135974835236</t>
+          <t>4500000383202608132236113522</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" s="0">
-        <v>49196385</v>
+        <v>49196439</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>平淡人生🌲</t>
+          <t>翰林世家京墨18240001035</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
@@ -7399,7 +7394,7 @@
       </c>
       <c r="G113" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:35</t>
+          <t>2026-08-13 21:32:18</t>
         </is>
       </c>
       <c r="H113" s="0" t="inlineStr">
@@ -7429,17 +7424,17 @@
       </c>
       <c r="M113" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608136587117638</t>
+          <t>4500000315202608131410776307</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" s="0">
-        <v>49196384</v>
+        <v>49196437</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>眼镜灯饰城3楼76号15923959748</t>
+          <t>悦朵宝贝</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
@@ -7464,7 +7459,7 @@
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:34</t>
+          <t>2026-08-13 21:32:06</t>
         </is>
       </c>
       <c r="H114" s="0" t="inlineStr">
@@ -7494,17 +7489,17 @@
       </c>
       <c r="M114" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608139966140440</t>
+          <t>4500000343202608135681746747</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" s="0">
-        <v>49196383</v>
+        <v>49196435</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>喜枝</t>
+          <t>我的幸福</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
@@ -7529,7 +7524,7 @@
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>2026-08-13 21:31:45</t>
+          <t>2026-08-13 21:32:23</t>
         </is>
       </c>
       <c r="H115" s="0" t="inlineStr">
@@ -7559,17 +7554,17 @@
       </c>
       <c r="M115" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608138694510811</t>
+          <t>4500000331202608138821842807</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" s="0">
-        <v>49155446</v>
+        <v>49196433</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>笑口常开</t>
+          <t>程胜英</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
@@ -7594,7 +7589,7 @@
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:36:06</t>
+          <t>2026-08-13 21:32:33</t>
         </is>
       </c>
       <c r="H116" s="0" t="inlineStr">
@@ -7624,17 +7619,17 @@
       </c>
       <c r="M116" s="0" t="inlineStr">
         <is>
-          <t>4500000376202608121856487760</t>
+          <t>4500000338202608136558136840</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="0">
-        <v>49155389</v>
+        <v>49196424</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>奥普郭彦丽13937990394</t>
+          <t>甘峰源奶奶</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
@@ -7659,7 +7654,7 @@
       </c>
       <c r="G117" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:44</t>
+          <t>2026-08-13 21:32:16</t>
         </is>
       </c>
       <c r="H117" s="0" t="inlineStr">
@@ -7689,17 +7684,17 @@
       </c>
       <c r="M117" s="0" t="inlineStr">
         <is>
-          <t>4500000324202608124582542642</t>
+          <t>4500000374202608139681236972</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" s="0">
-        <v>49155374</v>
+        <v>49196412</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>流星雨文华</t>
+          <t>贝贝老妈</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
@@ -7724,7 +7719,7 @@
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:26</t>
+          <t>2026-08-13 21:31:49</t>
         </is>
       </c>
       <c r="H118" s="0" t="inlineStr">
@@ -7754,17 +7749,17 @@
       </c>
       <c r="M118" s="0" t="inlineStr">
         <is>
-          <t>4500000377202608121430434820</t>
+          <t>4500000360202608138627203805</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" s="0">
-        <v>49155368</v>
+        <v>49196406</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>笑对人生</t>
+          <t>过好每一天</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
@@ -7789,7 +7784,7 @@
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:56</t>
+          <t>2026-08-13 21:31:55</t>
         </is>
       </c>
       <c r="H119" s="0" t="inlineStr">
@@ -7819,17 +7814,17 @@
       </c>
       <c r="M119" s="0" t="inlineStr">
         <is>
-          <t>4500000316202608126193240482</t>
+          <t>4500000384202608139484061741</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="0">
-        <v>49155365</v>
+        <v>49196403</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>秀</t>
+          <t>迪迪</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
@@ -7854,7 +7849,7 @@
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:41</t>
+          <t>2026-08-13 21:31:58</t>
         </is>
       </c>
       <c r="H120" s="0" t="inlineStr">
@@ -7884,17 +7879,17 @@
       </c>
       <c r="M120" s="0" t="inlineStr">
         <is>
-          <t>4500000363202608121090433848</t>
+          <t>4500000326202608138209731181</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" s="0">
-        <v>49155364</v>
+        <v>49196399</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>冯衣制版18966913385</t>
+          <t>境随心转</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
@@ -7919,7 +7914,7 @@
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:35:09</t>
+          <t>2026-08-13 21:31:47</t>
         </is>
       </c>
       <c r="H121" s="0" t="inlineStr">
@@ -7949,17 +7944,17 @@
       </c>
       <c r="M121" s="0" t="inlineStr">
         <is>
-          <t>4500000348202608122728123344</t>
+          <t>4500000380202608138946210876</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="0">
-        <v>49155363</v>
+        <v>49196391</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>平安</t>
+          <t>💖海霞💖</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
@@ -7984,7 +7979,7 @@
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:54</t>
+          <t>2026-08-13 21:32:01</t>
         </is>
       </c>
       <c r="H122" s="0" t="inlineStr">
@@ -8014,17 +8009,17 @@
       </c>
       <c r="M122" s="0" t="inlineStr">
         <is>
-          <t>4500000320202608128317430099</t>
+          <t>4500000326202608133672869122</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" s="0">
-        <v>49155361</v>
+        <v>49196390</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>春华秋实</t>
+          <t>翠翠</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
@@ -8049,7 +8044,7 @@
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:48</t>
+          <t>2026-08-13 21:31:38</t>
         </is>
       </c>
       <c r="H123" s="0" t="inlineStr">
@@ -8079,17 +8074,22 @@
       </c>
       <c r="M123" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608121174096033</t>
+          <t>4500000351202608139683947334</t>
+        </is>
+      </c>
+      <c r="N123" s="0" t="inlineStr">
+        <is>
+          <t>广州</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="0">
-        <v>49155359</v>
+        <v>49196389</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>春梅。</t>
+          <t>漫步繁华街</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:36</t>
+          <t>2026-08-13 21:32:39</t>
         </is>
       </c>
       <c r="H124" s="0" t="inlineStr">
@@ -8144,17 +8144,17 @@
       </c>
       <c r="M124" s="0" t="inlineStr">
         <is>
-          <t>4500000374202608123637081551</t>
+          <t>4500000375202608135974835236</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" s="0">
-        <v>49155344</v>
+        <v>49196385</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>自由人生</t>
+          <t>平淡人生🌲</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:25</t>
+          <t>2026-08-13 21:31:35</t>
         </is>
       </c>
       <c r="H125" s="0" t="inlineStr">
@@ -8209,17 +8209,17 @@
       </c>
       <c r="M125" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608129865186226</t>
+          <t>4500000359202608136587117638</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="0">
-        <v>49155337</v>
+        <v>49196384</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>红红</t>
+          <t>眼镜灯饰城3楼76号15923959748</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="G126" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:50</t>
+          <t>2026-08-13 21:31:34</t>
         </is>
       </c>
       <c r="H126" s="0" t="inlineStr">
@@ -8274,17 +8274,17 @@
       </c>
       <c r="M126" s="0" t="inlineStr">
         <is>
-          <t>4500000327202608125530964720</t>
+          <t>4500000333202608139966140440</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" s="0">
-        <v>49155330</v>
+        <v>49196383</v>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>徐淑香</t>
+          <t>喜枝</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="G127" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:20</t>
+          <t>2026-08-13 21:31:45</t>
         </is>
       </c>
       <c r="H127" s="0" t="inlineStr">
@@ -8339,17 +8339,17 @@
       </c>
       <c r="M127" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608124983971576</t>
+          <t>4500000333202608138694510811</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="0">
-        <v>49155314</v>
+        <v>49155446</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>H叶</t>
+          <t>笑口常开</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:57</t>
+          <t>2026-08-12 21:36:06</t>
         </is>
       </c>
       <c r="H128" s="0" t="inlineStr">
@@ -8404,17 +8404,17 @@
       </c>
       <c r="M128" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608128162955185</t>
+          <t>4500000376202608121856487760</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" s="0">
-        <v>49155309</v>
+        <v>49155389</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>A0000刘氏修脚红姐</t>
+          <t>奥普郭彦丽13937990394</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:47</t>
+          <t>2026-08-12 21:35:44</t>
         </is>
       </c>
       <c r="H129" s="0" t="inlineStr">
@@ -8469,17 +8469,17 @@
       </c>
       <c r="M129" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608127176361921</t>
+          <t>4500000324202608124582542642</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="0">
-        <v>49155304</v>
+        <v>49155374</v>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>万树红</t>
+          <t>流星雨文华</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:52</t>
+          <t>2026-08-12 21:35:26</t>
         </is>
       </c>
       <c r="H130" s="0" t="inlineStr">
@@ -8534,17 +8534,17 @@
       </c>
       <c r="M130" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608123430987084</t>
+          <t>4500000377202608121430434820</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="0">
-        <v>49155293</v>
+        <v>49155368</v>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>往事如烟</t>
+          <t>笑对人生</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:33</t>
+          <t>2026-08-12 21:34:56</t>
         </is>
       </c>
       <c r="H131" s="0" t="inlineStr">
@@ -8599,17 +8599,17 @@
       </c>
       <c r="M131" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608121388094535</t>
+          <t>4500000316202608126193240482</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="0">
-        <v>49155283</v>
+        <v>49155365</v>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>雪洁</t>
+          <t>秀</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:27</t>
+          <t>2026-08-12 21:34:41</t>
         </is>
       </c>
       <c r="H132" s="0" t="inlineStr">
@@ -8664,17 +8664,17 @@
       </c>
       <c r="M132" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608125072492429</t>
+          <t>4500000363202608121090433848</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="0">
-        <v>49155274</v>
+        <v>49155364</v>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>文英</t>
+          <t>冯衣制版18966913385</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:24</t>
+          <t>2026-08-12 21:35:09</t>
         </is>
       </c>
       <c r="H133" s="0" t="inlineStr">
@@ -8729,17 +8729,17 @@
       </c>
       <c r="M133" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608127495955817</t>
+          <t>4500000348202608122728123344</t>
         </is>
       </c>
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="0">
-        <v>49155273</v>
+        <v>49155363</v>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>宫本江</t>
+          <t>平安</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:34:54</t>
         </is>
       </c>
       <c r="H134" s="0" t="inlineStr">
@@ -8794,17 +8794,17 @@
       </c>
       <c r="M134" s="0" t="inlineStr">
         <is>
-          <t>4500000346202608122111396208</t>
+          <t>4500000320202608128317430099</t>
         </is>
       </c>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="0">
-        <v>49155272</v>
+        <v>49155361</v>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>悠闲的人</t>
+          <t>春华秋实</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="G135" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:13</t>
+          <t>2026-08-12 21:34:48</t>
         </is>
       </c>
       <c r="H135" s="0" t="inlineStr">
@@ -8859,17 +8859,17 @@
       </c>
       <c r="M135" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608122303219210</t>
+          <t>4500000346202608121174096033</t>
         </is>
       </c>
     </row>
     <row r="136" spans="1:14">
       <c r="A136" s="0">
-        <v>49155271</v>
+        <v>49155359</v>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>幸福人生</t>
+          <t>春梅。</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:08</t>
+          <t>2026-08-12 21:34:36</t>
         </is>
       </c>
       <c r="H136" s="0" t="inlineStr">
@@ -8924,17 +8924,17 @@
       </c>
       <c r="M136" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608124799146350</t>
+          <t>4500000374202608123637081551</t>
         </is>
       </c>
     </row>
     <row r="137" spans="1:14">
       <c r="A137" s="0">
-        <v>49155270</v>
+        <v>49155344</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>雾里看花</t>
+          <t>自由人生</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:15</t>
+          <t>2026-08-12 21:34:25</t>
         </is>
       </c>
       <c r="H137" s="0" t="inlineStr">
@@ -8989,17 +8989,17 @@
       </c>
       <c r="M137" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608123995555310</t>
+          <t>4500000317202608129865186226</t>
         </is>
       </c>
     </row>
     <row r="138" spans="1:14">
       <c r="A138" s="0">
-        <v>49155266</v>
+        <v>49155337</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>清风绕指柔</t>
+          <t>红红</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:31</t>
+          <t>2026-08-12 21:34:50</t>
         </is>
       </c>
       <c r="H138" s="0" t="inlineStr">
@@ -9054,17 +9054,17 @@
       </c>
       <c r="M138" s="0" t="inlineStr">
         <is>
-          <t>4500000333202608127946689166</t>
+          <t>4500000327202608125530964720</t>
         </is>
       </c>
     </row>
     <row r="139" spans="1:14">
       <c r="A139" s="0">
-        <v>49155265</v>
+        <v>49155330</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>心想事成南无阿弥陀佛</t>
+          <t>徐淑香</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G139" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:42</t>
+          <t>2026-08-12 21:34:20</t>
         </is>
       </c>
       <c r="H139" s="0" t="inlineStr">
@@ -9119,17 +9119,17 @@
       </c>
       <c r="M139" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608126996164764</t>
+          <t>4500000359202608124983971576</t>
         </is>
       </c>
     </row>
     <row r="140" spans="1:14">
       <c r="A140" s="0">
-        <v>49155264</v>
+        <v>49155314</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>刘凤辉</t>
+          <t>H叶</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="G140" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:33:57</t>
         </is>
       </c>
       <c r="H140" s="0" t="inlineStr">
@@ -9184,17 +9184,17 @@
       </c>
       <c r="M140" s="0" t="inlineStr">
         <is>
-          <t>4500000330202608124680304775</t>
+          <t>4500000322202608128162955185</t>
         </is>
       </c>
     </row>
     <row r="141" spans="1:14">
       <c r="A141" s="0">
-        <v>49155263</v>
+        <v>49155309</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>朱叶</t>
+          <t>A0000刘氏修脚红姐</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:18</t>
+          <t>2026-08-12 21:33:47</t>
         </is>
       </c>
       <c r="H141" s="0" t="inlineStr">
@@ -9249,17 +9249,17 @@
       </c>
       <c r="M141" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608124445297817</t>
+          <t>4500000333202608127176361921</t>
         </is>
       </c>
     </row>
     <row r="142" spans="1:14">
       <c r="A142" s="0">
-        <v>49155253</v>
+        <v>49155304</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>一顺百顺。好运来</t>
+          <t>万树红</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="G142" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:51</t>
+          <t>2026-08-12 21:33:52</t>
         </is>
       </c>
       <c r="H142" s="0" t="inlineStr">
@@ -9314,17 +9314,17 @@
       </c>
       <c r="M142" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608122909608257</t>
+          <t>4500000379202608123430987084</t>
         </is>
       </c>
     </row>
     <row r="143" spans="1:14">
       <c r="A143" s="0">
-        <v>49155246</v>
+        <v>49155293</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>陈桂芳</t>
+          <t>往事如烟</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:14</t>
+          <t>2026-08-12 21:33:33</t>
         </is>
       </c>
       <c r="H143" s="0" t="inlineStr">
@@ -9379,17 +9379,17 @@
       </c>
       <c r="M143" s="0" t="inlineStr">
         <is>
-          <t>4500000378202608126828589764</t>
+          <t>4500000360202608121388094535</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:14">
       <c r="A144" s="0">
-        <v>49155234</v>
+        <v>49155283</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>黄仲芬15683592716</t>
+          <t>雪洁</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:27</t>
         </is>
       </c>
       <c r="H144" s="0" t="inlineStr">
@@ -9444,17 +9444,17 @@
       </c>
       <c r="M144" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608129237945248</t>
+          <t>4500000369202608125072492429</t>
         </is>
       </c>
     </row>
     <row r="145" spans="1:14">
       <c r="A145" s="0">
-        <v>49155233</v>
+        <v>49155274</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>幸福姐赵会玲</t>
+          <t>文英</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:34:04</t>
+          <t>2026-08-12 21:33:24</t>
         </is>
       </c>
       <c r="H145" s="0" t="inlineStr">
@@ -9509,17 +9509,17 @@
       </c>
       <c r="M145" s="0" t="inlineStr">
         <is>
-          <t>4500000317202608128379976752</t>
+          <t>4500000373202608127495955817</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146" s="0">
-        <v>49155230</v>
+        <v>49155273</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>锦鲤果果</t>
+          <t>宫本江</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:20</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H146" s="0" t="inlineStr">
@@ -9574,17 +9574,17 @@
       </c>
       <c r="M146" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608129199323858</t>
+          <t>4500000346202608122111396208</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:14">
       <c r="A147" s="0">
-        <v>49155226</v>
+        <v>49155272</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>戎戎</t>
+          <t>悠闲的人</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:05</t>
+          <t>2026-08-12 21:33:13</t>
         </is>
       </c>
       <c r="H147" s="0" t="inlineStr">
@@ -9639,17 +9639,17 @@
       </c>
       <c r="M147" s="0" t="inlineStr">
         <is>
-          <t>4500000331202608125827170254</t>
+          <t>4500000331202608122303219210</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:14">
       <c r="A148" s="0">
-        <v>49155220</v>
+        <v>49155271</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>阿玉</t>
+          <t>幸福人生</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:16</t>
+          <t>2026-08-12 21:34:08</t>
         </is>
       </c>
       <c r="H148" s="0" t="inlineStr">
@@ -9704,17 +9704,17 @@
       </c>
       <c r="M148" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608129272259118</t>
+          <t>4500000333202608124799146350</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:14">
       <c r="A149" s="0">
-        <v>49155219</v>
+        <v>49155270</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>沉淀、</t>
+          <t>雾里看花</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:15</t>
         </is>
       </c>
       <c r="H149" s="0" t="inlineStr">
@@ -9769,17 +9769,17 @@
       </c>
       <c r="M149" s="0" t="inlineStr">
         <is>
-          <t>4500000372202608124305947387</t>
+          <t>4500000331202608123995555310</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150" s="0">
-        <v>49155216</v>
+        <v>49155266</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>晴天</t>
+          <t>清风绕指柔</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:07</t>
+          <t>2026-08-12 21:33:31</t>
         </is>
       </c>
       <c r="H150" s="0" t="inlineStr">
@@ -9834,17 +9834,17 @@
       </c>
       <c r="M150" s="0" t="inlineStr">
         <is>
-          <t>4500000334202608122833385690</t>
+          <t>4500000333202608127946689166</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:14">
       <c r="A151" s="0">
-        <v>49155210</v>
+        <v>49155265</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>开正商行</t>
+          <t>心想事成南无阿弥陀佛</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:33:42</t>
         </is>
       </c>
       <c r="H151" s="0" t="inlineStr">
@@ -9899,17 +9899,17 @@
       </c>
       <c r="M151" s="0" t="inlineStr">
         <is>
-          <t>4500000348202608127466098812</t>
+          <t>4500000330202608126996164764</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:14">
       <c r="A152" s="0">
-        <v>49155208</v>
+        <v>49155264</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>傻傻的幸福</t>
+          <t>刘凤辉</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H152" s="0" t="inlineStr">
@@ -9964,17 +9964,17 @@
       </c>
       <c r="M152" s="0" t="inlineStr">
         <is>
-          <t>4500000378202608122593720010</t>
+          <t>4500000330202608124680304775</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="0">
-        <v>49155205</v>
+        <v>49155263</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>你好</t>
+          <t>朱叶</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:59</t>
+          <t>2026-08-12 21:33:18</t>
         </is>
       </c>
       <c r="H153" s="0" t="inlineStr">
@@ -10029,17 +10029,17 @@
       </c>
       <c r="M153" s="0" t="inlineStr">
         <is>
-          <t>4500000335202608122478222937</t>
+          <t>4500000345202608124445297817</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:14">
       <c r="A154" s="0">
-        <v>49155203</v>
+        <v>49155253</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>一生有你</t>
+          <t>一顺百顺。好运来</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:51</t>
         </is>
       </c>
       <c r="H154" s="0" t="inlineStr">
@@ -10094,17 +10094,17 @@
       </c>
       <c r="M154" s="0" t="inlineStr">
         <is>
-          <t>4500000369202608129324316511</t>
+          <t>4500000326202608122909608257</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:14">
       <c r="A155" s="0">
-        <v>49155200</v>
+        <v>49155246</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>陈桂芳</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:09</t>
+          <t>2026-08-12 21:33:14</t>
         </is>
       </c>
       <c r="H155" s="0" t="inlineStr">
@@ -10159,17 +10159,17 @@
       </c>
       <c r="M155" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608125850014769</t>
+          <t>4500000378202608126828589764</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:14">
       <c r="A156" s="0">
-        <v>49155197</v>
+        <v>49155234</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>桂芝改名叫张淑玮</t>
+          <t>黄仲芬15683592716</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:00</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H156" s="0" t="inlineStr">
@@ -10224,17 +10224,17 @@
       </c>
       <c r="M156" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608121228274851</t>
+          <t>4500000325202608129237945248</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:14">
       <c r="A157" s="0">
-        <v>49155194</v>
+        <v>49155233</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>自强不息</t>
+          <t>幸福姐赵会玲</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:14</t>
+          <t>2026-08-12 21:34:04</t>
         </is>
       </c>
       <c r="H157" s="0" t="inlineStr">
@@ -10289,17 +10289,17 @@
       </c>
       <c r="M157" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608124140031616</t>
+          <t>4500000317202608128379976752</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:14">
       <c r="A158" s="0">
-        <v>49155192</v>
+        <v>49155230</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>时光如水</t>
+          <t>锦鲤果果</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:03</t>
+          <t>2026-08-12 21:33:20</t>
         </is>
       </c>
       <c r="H158" s="0" t="inlineStr">
@@ -10354,17 +10354,17 @@
       </c>
       <c r="M158" s="0" t="inlineStr">
         <is>
-          <t>4500000364202608128865933230</t>
+          <t>4500000322202608129199323858</t>
         </is>
       </c>
     </row>
     <row r="159" spans="1:14">
       <c r="A159" s="0">
-        <v>49155187</v>
+        <v>49155226</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>张丽</t>
+          <t>戎戎</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:33:05</t>
         </is>
       </c>
       <c r="H159" s="0" t="inlineStr">
@@ -10419,17 +10419,17 @@
       </c>
       <c r="M159" s="0" t="inlineStr">
         <is>
-          <t>4500000334202608125275144248</t>
+          <t>4500000331202608125827170254</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:14">
       <c r="A160" s="0">
-        <v>49155186</v>
+        <v>49155220</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>星辰</t>
+          <t>阿玉</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:52</t>
+          <t>2026-08-12 21:33:16</t>
         </is>
       </c>
       <c r="H160" s="0" t="inlineStr">
@@ -10484,17 +10484,17 @@
       </c>
       <c r="M160" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608121378976306</t>
+          <t>4500000345202608129272259118</t>
         </is>
       </c>
     </row>
     <row r="161" spans="1:14">
       <c r="A161" s="0">
-        <v>49155185</v>
+        <v>49155219</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>天津温室大棚光伏厂家18920981728</t>
+          <t>沉淀、</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:32</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H161" s="0" t="inlineStr">
@@ -10549,17 +10549,17 @@
       </c>
       <c r="M161" s="0" t="inlineStr">
         <is>
-          <t>4500000318202608125631581660</t>
+          <t>4500000372202608124305947387</t>
         </is>
       </c>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="0">
-        <v>49155184</v>
+        <v>49155216</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>惠民</t>
+          <t>晴天</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:08</t>
+          <t>2026-08-12 21:33:07</t>
         </is>
       </c>
       <c r="H162" s="0" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="M162" s="0" t="inlineStr">
         <is>
-          <t>4500000355202608121279528970</t>
+          <t>4500000334202608122833385690</t>
         </is>
       </c>
     </row>
     <row r="163" spans="1:14">
       <c r="A163" s="0">
-        <v>49155180</v>
+        <v>49155210</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>常青树</t>
+          <t>开正商行</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="G163" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:06</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H163" s="0" t="inlineStr">
@@ -10679,17 +10679,17 @@
       </c>
       <c r="M163" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608125426925788</t>
+          <t>4500000348202608127466098812</t>
         </is>
       </c>
     </row>
     <row r="164" spans="1:14">
       <c r="A164" s="0">
-        <v>49155178</v>
+        <v>49155208</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>玉伟</t>
+          <t>傻傻的幸福</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="G164" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:07</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H164" s="0" t="inlineStr">
@@ -10744,17 +10744,17 @@
       </c>
       <c r="M164" s="0" t="inlineStr">
         <is>
-          <t>4500000364202608125205677586</t>
+          <t>4500000378202608122593720010</t>
         </is>
       </c>
     </row>
     <row r="165" spans="1:14">
       <c r="A165" s="0">
-        <v>49155171</v>
+        <v>49155205</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>秦晓娟～中医五官排毒</t>
+          <t>你好</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="G165" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:02</t>
+          <t>2026-08-12 21:32:59</t>
         </is>
       </c>
       <c r="H165" s="0" t="inlineStr">
@@ -10809,17 +10809,17 @@
       </c>
       <c r="M165" s="0" t="inlineStr">
         <is>
-          <t>4500000365202608129265074581</t>
+          <t>4500000335202608122478222937</t>
         </is>
       </c>
     </row>
     <row r="166" spans="1:14">
       <c r="A166" s="0">
-        <v>49155167</v>
+        <v>49155203</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>水琴</t>
+          <t>一生有你</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="G166" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H166" s="0" t="inlineStr">
@@ -10874,17 +10874,17 @@
       </c>
       <c r="M166" s="0" t="inlineStr">
         <is>
-          <t>4500000315202608128554791016</t>
+          <t>4500000369202608129324316511</t>
         </is>
       </c>
     </row>
     <row r="167" spans="1:14">
       <c r="A167" s="0">
-        <v>49155163</v>
+        <v>49155200</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>祥云ಠ_ಠ</t>
+          <t>618</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="G167" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:56</t>
+          <t>2026-08-12 21:33:09</t>
         </is>
       </c>
       <c r="H167" s="0" t="inlineStr">
@@ -10939,17 +10939,17 @@
       </c>
       <c r="M167" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608126804876906</t>
+          <t>4500000384202608125850014769</t>
         </is>
       </c>
     </row>
     <row r="168" spans="1:14">
       <c r="A168" s="0">
-        <v>49155162</v>
+        <v>49155197</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>雪绒花</t>
+          <t>桂芝改名叫张淑玮</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
@@ -11004,17 +11004,17 @@
       </c>
       <c r="M168" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608122943306781</t>
+          <t>4500000351202608121228274851</t>
         </is>
       </c>
     </row>
     <row r="169" spans="1:14">
       <c r="A169" s="0">
-        <v>49155161</v>
+        <v>49155194</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>        糖果</t>
+          <t>自强不息</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:52</t>
+          <t>2026-08-12 21:33:14</t>
         </is>
       </c>
       <c r="H169" s="0" t="inlineStr">
@@ -11069,17 +11069,17 @@
       </c>
       <c r="M169" s="0" t="inlineStr">
         <is>
-          <t>4500000384202608121712400624</t>
+          <t>4500000356202608124140031616</t>
         </is>
       </c>
     </row>
     <row r="170" spans="1:14">
       <c r="A170" s="0">
-        <v>49155157</v>
+        <v>49155192</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>流失的岁月</t>
+          <t>时光如水</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="G170" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:11</t>
+          <t>2026-08-12 21:33:03</t>
         </is>
       </c>
       <c r="H170" s="0" t="inlineStr">
@@ -11134,17 +11134,17 @@
       </c>
       <c r="M170" s="0" t="inlineStr">
         <is>
-          <t>4500000379202608126379751055</t>
+          <t>4500000364202608128865933230</t>
         </is>
       </c>
     </row>
     <row r="171" spans="1:14">
       <c r="A171" s="0">
-        <v>49155152</v>
+        <v>49155187</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>夏末幽荷</t>
+          <t>张丽</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="G171" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H171" s="0" t="inlineStr">
@@ -11199,17 +11199,17 @@
       </c>
       <c r="M171" s="0" t="inlineStr">
         <is>
-          <t>4500000337202608128669470764</t>
+          <t>4500000334202608125275144248</t>
         </is>
       </c>
     </row>
     <row r="172" spans="1:14">
       <c r="A172" s="0">
-        <v>49155150</v>
+        <v>49155186</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>药曼</t>
+          <t>星辰</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:32:52</t>
         </is>
       </c>
       <c r="H172" s="0" t="inlineStr">
@@ -11264,17 +11264,17 @@
       </c>
       <c r="M172" s="0" t="inlineStr">
         <is>
-          <t>4500000345202608127294126669</t>
+          <t>4500000373202608121378976306</t>
         </is>
       </c>
     </row>
     <row r="173" spans="1:14">
       <c r="A173" s="0">
-        <v>49155149</v>
+        <v>49155185</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>🌺 谭谭🌺</t>
+          <t>天津温室大棚光伏厂家18920981728</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:58</t>
+          <t>2026-08-12 21:33:32</t>
         </is>
       </c>
       <c r="H173" s="0" t="inlineStr">
@@ -11329,17 +11329,17 @@
       </c>
       <c r="M173" s="0" t="inlineStr">
         <is>
-          <t>4500000350202608121029117778</t>
+          <t>4500000318202608125631581660</t>
         </is>
       </c>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="0">
-        <v>49155148</v>
+        <v>49155184</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>王玉(邮局对面卖手机)</t>
+          <t>惠民</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:33:08</t>
         </is>
       </c>
       <c r="H174" s="0" t="inlineStr">
@@ -11394,17 +11394,17 @@
       </c>
       <c r="M174" s="0" t="inlineStr">
         <is>
-          <t>4500000342202608126218721690</t>
+          <t>4500000355202608121279528970</t>
         </is>
       </c>
     </row>
     <row r="175" spans="1:14">
       <c r="A175" s="0">
-        <v>49155147</v>
+        <v>49155180</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>美好夕阳</t>
+          <t>常青树</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:33:06</t>
         </is>
       </c>
       <c r="H175" s="0" t="inlineStr">
@@ -11459,17 +11459,17 @@
       </c>
       <c r="M175" s="0" t="inlineStr">
         <is>
-          <t>4500000343202608128224202725</t>
+          <t>4500000357202608125426925788</t>
         </is>
       </c>
     </row>
     <row r="176" spans="1:14">
       <c r="A176" s="0">
-        <v>49155145</v>
+        <v>49155178</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>平凡</t>
+          <t>玉伟</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:57</t>
+          <t>2026-08-12 21:33:07</t>
         </is>
       </c>
       <c r="H176" s="0" t="inlineStr">
@@ -11524,17 +11524,17 @@
       </c>
       <c r="M176" s="0" t="inlineStr">
         <is>
-          <t>4500000359202608122476247171</t>
+          <t>4500000364202608125205677586</t>
         </is>
       </c>
     </row>
     <row r="177" spans="1:14">
       <c r="A177" s="0">
-        <v>49155143</v>
+        <v>49155171</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>唐洪</t>
+          <t>秦晓娟～中医五官排毒</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:45</t>
+          <t>2026-08-12 21:33:02</t>
         </is>
       </c>
       <c r="H177" s="0" t="inlineStr">
@@ -11589,17 +11589,17 @@
       </c>
       <c r="M177" s="0" t="inlineStr">
         <is>
-          <t>4500000350202608125309483592</t>
+          <t>4500000365202608129265074581</t>
         </is>
       </c>
     </row>
     <row r="178" spans="1:14">
       <c r="A178" s="0">
-        <v>49155140</v>
+        <v>49155167</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>浅笑</t>
+          <t>水琴</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:57</t>
+          <t>2026-08-12 21:32:54</t>
         </is>
       </c>
       <c r="H178" s="0" t="inlineStr">
@@ -11654,17 +11654,17 @@
       </c>
       <c r="M178" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608123442658613</t>
+          <t>4500000315202608128554791016</t>
         </is>
       </c>
     </row>
     <row r="179" spans="1:14">
       <c r="A179" s="0">
-        <v>49155137</v>
+        <v>49155163</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>梅放芳香</t>
+          <t>祥云ಠ_ಠ</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:59</t>
+          <t>2026-08-12 21:32:56</t>
         </is>
       </c>
       <c r="H179" s="0" t="inlineStr">
@@ -11719,17 +11719,17 @@
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
-          <t>4500000356202608127843962862</t>
+          <t>4500000344202608126804876906</t>
         </is>
       </c>
     </row>
     <row r="180" spans="1:14">
       <c r="A180" s="0">
-        <v>49155135</v>
+        <v>49155162</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>吴素华</t>
+          <t>雪绒花</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:33:00</t>
         </is>
       </c>
       <c r="H180" s="0" t="inlineStr">
@@ -11784,17 +11784,17 @@
       </c>
       <c r="M180" s="0" t="inlineStr">
         <is>
-          <t>4500000339202608124292727044</t>
+          <t>4500000343202608122943306781</t>
         </is>
       </c>
     </row>
     <row r="181" spans="1:14">
       <c r="A181" s="0">
-        <v>49155132</v>
+        <v>49155161</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>苗斯妤铂金牌月嫂催乳18839028160</t>
+          <t>        糖果</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="G181" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:46</t>
+          <t>2026-08-12 21:32:52</t>
         </is>
       </c>
       <c r="H181" s="0" t="inlineStr">
@@ -11849,17 +11849,17 @@
       </c>
       <c r="M181" s="0" t="inlineStr">
         <is>
-          <t>4500000322202608123141162109</t>
+          <t>4500000384202608121712400624</t>
         </is>
       </c>
     </row>
     <row r="182" spans="1:14">
       <c r="A182" s="0">
-        <v>49155131</v>
+        <v>49155157</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>瓷星.</t>
+          <t>流失的岁月</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="G182" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:50</t>
+          <t>2026-08-12 21:33:11</t>
         </is>
       </c>
       <c r="H182" s="0" t="inlineStr">
@@ -11914,17 +11914,17 @@
       </c>
       <c r="M182" s="0" t="inlineStr">
         <is>
-          <t>4500000383202608121548709297</t>
+          <t>4500000379202608126379751055</t>
         </is>
       </c>
     </row>
     <row r="183" spans="1:14">
       <c r="A183" s="0">
-        <v>49155129</v>
+        <v>49155152</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>妈咪宝贝</t>
+          <t>夏末幽荷</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="G183" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:42</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H183" s="0" t="inlineStr">
@@ -11979,17 +11979,17 @@
       </c>
       <c r="M183" s="0" t="inlineStr">
         <is>
-          <t>4500000347202608127726342481</t>
+          <t>4500000337202608128669470764</t>
         </is>
       </c>
     </row>
     <row r="184" spans="1:14">
       <c r="A184" s="0">
-        <v>49155128</v>
+        <v>49155150</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>愿结天下有缘人</t>
+          <t>药曼</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="G184" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:46</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H184" s="0" t="inlineStr">
@@ -12044,17 +12044,17 @@
       </c>
       <c r="M184" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608128699617090</t>
+          <t>4500000345202608127294126669</t>
         </is>
       </c>
     </row>
     <row r="185" spans="1:14">
       <c r="A185" s="0">
-        <v>49155124</v>
+        <v>49155149</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>勿忘初心</t>
+          <t>🌺 谭谭🌺</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="G185" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:49</t>
+          <t>2026-08-12 21:32:58</t>
         </is>
       </c>
       <c r="H185" s="0" t="inlineStr">
@@ -12109,17 +12109,17 @@
       </c>
       <c r="M185" s="0" t="inlineStr">
         <is>
-          <t>4500000373202608128217629837</t>
+          <t>4500000350202608121029117778</t>
         </is>
       </c>
     </row>
     <row r="186" spans="1:14">
       <c r="A186" s="0">
-        <v>49155123</v>
+        <v>49155148</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>芳草天涯</t>
+          <t>王玉(邮局对面卖手机)</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="G186" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:32</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H186" s="0" t="inlineStr">
@@ -12174,22 +12174,17 @@
       </c>
       <c r="M186" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608123653997556</t>
-        </is>
-      </c>
-      <c r="N186" s="0" t="inlineStr">
-        <is>
-          <t>合肥</t>
+          <t>4500000342202608126218721690</t>
         </is>
       </c>
     </row>
     <row r="187" spans="1:14">
       <c r="A187" s="0">
-        <v>49155120</v>
+        <v>49155147</v>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>记忆中的你</t>
+          <t>美好夕阳</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
@@ -12214,7 +12209,7 @@
       </c>
       <c r="G187" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:53</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H187" s="0" t="inlineStr">
@@ -12244,17 +12239,17 @@
       </c>
       <c r="M187" s="0" t="inlineStr">
         <is>
-          <t>4500000326202608124401684219</t>
+          <t>4500000343202608128224202725</t>
         </is>
       </c>
     </row>
     <row r="188" spans="1:14">
       <c r="A188" s="0">
-        <v>49155114</v>
+        <v>49155145</v>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>微笑取暖</t>
+          <t>平凡</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
@@ -12279,7 +12274,7 @@
       </c>
       <c r="G188" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:33:38</t>
+          <t>2026-08-12 21:32:57</t>
         </is>
       </c>
       <c r="H188" s="0" t="inlineStr">
@@ -12309,17 +12304,17 @@
       </c>
       <c r="M188" s="0" t="inlineStr">
         <is>
-          <t>4500000325202608121874803628</t>
+          <t>4500000359202608122476247171</t>
         </is>
       </c>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="0">
-        <v>49155112</v>
+        <v>49155143</v>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>净心李芸</t>
+          <t>唐洪</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
@@ -12344,7 +12339,7 @@
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:33</t>
+          <t>2026-08-12 21:32:45</t>
         </is>
       </c>
       <c r="H189" s="0" t="inlineStr">
@@ -12374,17 +12369,17 @@
       </c>
       <c r="M189" s="0" t="inlineStr">
         <is>
-          <t>4500000351202608126115898528</t>
+          <t>4500000350202608125309483592</t>
         </is>
       </c>
     </row>
     <row r="190" spans="1:14">
       <c r="A190" s="0">
-        <v>49155108</v>
+        <v>49155140</v>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>衡澜</t>
+          <t>浅笑</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
@@ -12409,7 +12404,7 @@
       </c>
       <c r="G190" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:32</t>
+          <t>2026-08-12 21:32:57</t>
         </is>
       </c>
       <c r="H190" s="0" t="inlineStr">
@@ -12439,17 +12434,17 @@
       </c>
       <c r="M190" s="0" t="inlineStr">
         <is>
-          <t>4500000360202608128833814214</t>
+          <t>4500000360202608123442658613</t>
         </is>
       </c>
     </row>
     <row r="191" spans="1:14">
       <c r="A191" s="0">
-        <v>49155098</v>
+        <v>49155137</v>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>珂</t>
+          <t>梅放芳香</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
@@ -12474,7 +12469,7 @@
       </c>
       <c r="G191" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:39</t>
+          <t>2026-08-12 21:32:59</t>
         </is>
       </c>
       <c r="H191" s="0" t="inlineStr">
@@ -12504,17 +12499,17 @@
       </c>
       <c r="M191" s="0" t="inlineStr">
         <is>
-          <t>4500000344202608128766183266</t>
+          <t>4500000356202608127843962862</t>
         </is>
       </c>
     </row>
     <row r="192" spans="1:14">
       <c r="A192" s="0">
-        <v>49155095</v>
+        <v>49155135</v>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>平安保险~王家宝</t>
+          <t>吴素华</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
@@ -12539,7 +12534,7 @@
       </c>
       <c r="G192" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:54</t>
+          <t>2026-08-12 21:32:49</t>
         </is>
       </c>
       <c r="H192" s="0" t="inlineStr">
@@ -12569,17 +12564,17 @@
       </c>
       <c r="M192" s="0" t="inlineStr">
         <is>
-          <t>4500000321202608129139460754</t>
+          <t>4500000339202608124292727044</t>
         </is>
       </c>
     </row>
     <row r="193" spans="1:14">
       <c r="A193" s="0">
-        <v>49155092</v>
+        <v>49155132</v>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>爱情海</t>
+          <t>苗斯妤铂金牌月嫂催乳18839028160</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
@@ -12604,7 +12599,7 @@
       </c>
       <c r="G193" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:23</t>
+          <t>2026-08-12 21:32:46</t>
         </is>
       </c>
       <c r="H193" s="0" t="inlineStr">
@@ -12634,17 +12629,17 @@
       </c>
       <c r="M193" s="0" t="inlineStr">
         <is>
-          <t>4500000357202608125918396999</t>
+          <t>4500000322202608123141162109</t>
         </is>
       </c>
     </row>
     <row r="194" spans="1:14">
       <c r="A194" s="0">
-        <v>49155090</v>
+        <v>49155131</v>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>三月桃花</t>
+          <t>瓷星.</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
@@ -12669,7 +12664,7 @@
       </c>
       <c r="G194" s="0" t="inlineStr">
         <is>
-          <t>2026-08-12 21:32:26</t>
+          <t>2026-08-12 21:32:50</t>
         </is>
       </c>
       <c r="H194" s="0" t="inlineStr">
@@ -12699,70 +12694,855 @@
       </c>
       <c r="M194" s="0" t="inlineStr">
         <is>
-          <t>4500000382202608128744277768</t>
+          <t>4500000383202608121548709297</t>
         </is>
       </c>
     </row>
     <row r="195" spans="1:14">
       <c r="A195" s="0">
+        <v>49155129</v>
+      </c>
+      <c r="B195" s="0" t="inlineStr">
+        <is>
+          <t>妈咪宝贝</t>
+        </is>
+      </c>
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D195" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E195" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F195" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G195" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:42</t>
+        </is>
+      </c>
+      <c r="H195" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J195" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K195" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L195" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M195" s="0" t="inlineStr">
+        <is>
+          <t>4500000347202608127726342481</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" spans="1:14">
+      <c r="A196" s="0">
+        <v>49155128</v>
+      </c>
+      <c r="B196" s="0" t="inlineStr">
+        <is>
+          <t>愿结天下有缘人</t>
+        </is>
+      </c>
+      <c r="C196" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D196" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E196" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F196" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G196" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:46</t>
+        </is>
+      </c>
+      <c r="H196" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J196" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K196" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L196" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M196" s="0" t="inlineStr">
+        <is>
+          <t>4500000321202608128699617090</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" spans="1:14">
+      <c r="A197" s="0">
+        <v>49155124</v>
+      </c>
+      <c r="B197" s="0" t="inlineStr">
+        <is>
+          <t>勿忘初心</t>
+        </is>
+      </c>
+      <c r="C197" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D197" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E197" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F197" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G197" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:49</t>
+        </is>
+      </c>
+      <c r="H197" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J197" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K197" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L197" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M197" s="0" t="inlineStr">
+        <is>
+          <t>4500000373202608128217629837</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" spans="1:14">
+      <c r="A198" s="0">
+        <v>49155123</v>
+      </c>
+      <c r="B198" s="0" t="inlineStr">
+        <is>
+          <t>芳草天涯</t>
+        </is>
+      </c>
+      <c r="C198" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D198" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E198" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F198" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G198" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:32</t>
+        </is>
+      </c>
+      <c r="H198" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J198" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K198" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L198" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M198" s="0" t="inlineStr">
+        <is>
+          <t>4500000321202608123653997556</t>
+        </is>
+      </c>
+      <c r="N198" s="0" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" spans="1:14">
+      <c r="A199" s="0">
+        <v>49155120</v>
+      </c>
+      <c r="B199" s="0" t="inlineStr">
+        <is>
+          <t>记忆中的你</t>
+        </is>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D199" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E199" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F199" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G199" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:53</t>
+        </is>
+      </c>
+      <c r="H199" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J199" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K199" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L199" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M199" s="0" t="inlineStr">
+        <is>
+          <t>4500000326202608124401684219</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" spans="1:14">
+      <c r="A200" s="0">
+        <v>49155114</v>
+      </c>
+      <c r="B200" s="0" t="inlineStr">
+        <is>
+          <t>微笑取暖</t>
+        </is>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D200" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E200" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F200" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G200" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:33:38</t>
+        </is>
+      </c>
+      <c r="H200" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J200" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K200" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L200" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M200" s="0" t="inlineStr">
+        <is>
+          <t>4500000325202608121874803628</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" spans="1:14">
+      <c r="A201" s="0">
+        <v>49155112</v>
+      </c>
+      <c r="B201" s="0" t="inlineStr">
+        <is>
+          <t>净心李芸</t>
+        </is>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D201" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E201" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F201" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G201" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:33</t>
+        </is>
+      </c>
+      <c r="H201" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J201" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K201" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L201" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M201" s="0" t="inlineStr">
+        <is>
+          <t>4500000351202608126115898528</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" spans="1:14">
+      <c r="A202" s="0">
+        <v>49155108</v>
+      </c>
+      <c r="B202" s="0" t="inlineStr">
+        <is>
+          <t>衡澜</t>
+        </is>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D202" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E202" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F202" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G202" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:32</t>
+        </is>
+      </c>
+      <c r="H202" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J202" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K202" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L202" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M202" s="0" t="inlineStr">
+        <is>
+          <t>4500000360202608128833814214</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" spans="1:14">
+      <c r="A203" s="0">
+        <v>49155098</v>
+      </c>
+      <c r="B203" s="0" t="inlineStr">
+        <is>
+          <t>珂</t>
+        </is>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D203" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E203" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F203" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G203" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:39</t>
+        </is>
+      </c>
+      <c r="H203" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J203" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K203" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L203" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M203" s="0" t="inlineStr">
+        <is>
+          <t>4500000344202608128766183266</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" spans="1:14">
+      <c r="A204" s="0">
+        <v>49155095</v>
+      </c>
+      <c r="B204" s="0" t="inlineStr">
+        <is>
+          <t>平安保险~王家宝</t>
+        </is>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D204" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E204" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F204" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G204" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:54</t>
+        </is>
+      </c>
+      <c r="H204" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J204" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K204" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L204" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M204" s="0" t="inlineStr">
+        <is>
+          <t>4500000321202608129139460754</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" spans="1:14">
+      <c r="A205" s="0">
+        <v>49155092</v>
+      </c>
+      <c r="B205" s="0" t="inlineStr">
+        <is>
+          <t>爱情海</t>
+        </is>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D205" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E205" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F205" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G205" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:23</t>
+        </is>
+      </c>
+      <c r="H205" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J205" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K205" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L205" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M205" s="0" t="inlineStr">
+        <is>
+          <t>4500000357202608125918396999</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" spans="1:14">
+      <c r="A206" s="0">
+        <v>49155090</v>
+      </c>
+      <c r="B206" s="0" t="inlineStr">
+        <is>
+          <t>三月桃花</t>
+        </is>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D206" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E206" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F206" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G206" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-12 21:32:26</t>
+        </is>
+      </c>
+      <c r="H206" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J206" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K206" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L206" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M206" s="0" t="inlineStr">
+        <is>
+          <t>4500000382202608128744277768</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" spans="1:14">
+      <c r="A207" s="0">
         <v>49155088</v>
       </c>
-      <c r="B195" s="0" t="inlineStr">
+      <c r="B207" s="0" t="inlineStr">
         <is>
           <t>绘兰艺术李老师</t>
         </is>
       </c>
-      <c r="C195" s="0" t="inlineStr">
-        <is>
-          <t>【升级版】6天健康瑜伽体验营</t>
-        </is>
-      </c>
-      <c r="D195" s="0" t="inlineStr">
-        <is>
-          <t>训练营</t>
-        </is>
-      </c>
-      <c r="E195" s="0" t="inlineStr">
-        <is>
-          <t>￥1</t>
-        </is>
-      </c>
-      <c r="F195" s="0" t="inlineStr">
-        <is>
-          <t>￥1</t>
-        </is>
-      </c>
-      <c r="G195" s="0" t="inlineStr">
+      <c r="C207" s="0" t="inlineStr">
+        <is>
+          <t>【升级版】6天健康瑜伽体验营</t>
+        </is>
+      </c>
+      <c r="D207" s="0" t="inlineStr">
+        <is>
+          <t>训练营</t>
+        </is>
+      </c>
+      <c r="E207" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="F207" s="0" t="inlineStr">
+        <is>
+          <t>￥1</t>
+        </is>
+      </c>
+      <c r="G207" s="0" t="inlineStr">
         <is>
           <t>2026-08-12 21:32:20</t>
         </is>
       </c>
-      <c r="H195" s="0" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I195" s="0" t="inlineStr">
-        <is>
-          <t>彩虹-抖音1元瑜伽</t>
-        </is>
-      </c>
-      <c r="J195" s="0" t="inlineStr">
-        <is>
-          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
-        </is>
-      </c>
-      <c r="K195" s="0" t="inlineStr">
-        <is>
-          <t>微信支付</t>
-        </is>
-      </c>
-      <c r="L195" s="0" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="M195" s="0" t="inlineStr">
+      <c r="H207" s="0" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" s="0" t="inlineStr">
+        <is>
+          <t>彩虹-抖音1元瑜伽</t>
+        </is>
+      </c>
+      <c r="J207" s="0" t="inlineStr">
+        <is>
+          <t>【WY】瑜伽-气血皮肤（1元 · 支付）</t>
+        </is>
+      </c>
+      <c r="K207" s="0" t="inlineStr">
+        <is>
+          <t>微信支付</t>
+        </is>
+      </c>
+      <c r="L207" s="0" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="M207" s="0" t="inlineStr">
         <is>
           <t>4500000358202608128940402527</t>
         </is>
